--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\rogue_garden\ideas_ressources_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11E2328-07F8-4A99-BF26-2DC94715B3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B80963-27F1-4207-A1E7-FB5C39A15660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -2931,12 +2931,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2960,7 +2966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2996,6 +3002,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3335,7 +3347,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -3352,7 +3364,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -3369,7 +3381,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -3386,7 +3398,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -3403,7 +3415,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -3420,7 +3432,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -3437,7 +3449,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -3454,7 +3466,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -3488,7 +3500,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="11" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -3505,7 +3517,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -3522,7 +3534,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -3539,7 +3551,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -3556,7 +3568,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="11" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -3573,7 +3585,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -3590,7 +3602,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="11" t="s">
         <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -3991,14 +4003,14 @@
         <v>1</v>
       </c>
       <c r="E40" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -4032,7 +4044,7 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -4059,14 +4071,14 @@
         <v>1</v>
       </c>
       <c r="E44" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -6863,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B80963-27F1-4207-A1E7-FB5C39A15660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AD15FB-D231-42DF-9313-A842E545EF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -3619,7 +3619,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="11" t="s">
         <v>84</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -3636,7 +3636,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -3653,7 +3653,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="11" t="s">
         <v>73</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -3670,7 +3670,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="11" t="s">
         <v>85</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -3687,7 +3687,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="11" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3704,7 +3704,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="11" t="s">
         <v>81</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -3721,7 +3721,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="11" t="s">
         <v>65</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -3738,7 +3738,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -3755,7 +3755,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -3772,7 +3772,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="11" t="s">
         <v>69</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -3789,7 +3789,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -3806,7 +3806,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="11" t="s">
         <v>71</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -3823,7 +3823,7 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="11" t="s">
         <v>77</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -3840,7 +3840,7 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="11" t="s">
         <v>79</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -3857,7 +3857,7 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="11" t="s">
         <v>75</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -3874,7 +3874,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="11" t="s">
         <v>80</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -3891,7 +3891,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -3908,7 +3908,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="11" t="s">
         <v>86</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -3925,7 +3925,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="11" t="s">
         <v>76</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -3942,7 +3942,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="11" t="s">
         <v>78</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -3959,7 +3959,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="11" t="s">
         <v>83</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -3976,7 +3976,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="11" t="s">
         <v>67</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -4095,7 +4095,7 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -4112,7 +4112,7 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -4146,7 +4146,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="11" t="s">
         <v>58</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -4163,7 +4163,7 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="11" t="s">
         <v>62</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -4197,7 +4197,7 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -4214,7 +4214,7 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -4231,7 +4231,7 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="11" t="s">
         <v>28</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -4248,7 +4248,7 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -4265,7 +4265,7 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="11" t="s">
         <v>30</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -4282,7 +4282,7 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -4299,7 +4299,7 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -4316,7 +4316,7 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -4333,7 +4333,7 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -4360,14 +4360,14 @@
         <v>1</v>
       </c>
       <c r="E61" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -4380,11 +4380,11 @@
         <v>1</v>
       </c>
       <c r="G62" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -4401,7 +4401,7 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -4418,7 +4418,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="11" t="s">
         <v>47</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -4435,7 +4435,7 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="11" t="s">
         <v>48</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -4452,7 +4452,7 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -4469,7 +4469,7 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -4486,7 +4486,7 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="11" t="s">
         <v>57</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -4503,7 +4503,7 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="11" t="s">
         <v>50</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -4520,7 +4520,7 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="11" t="s">
         <v>52</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -4537,7 +4537,7 @@
       </c>
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -4557,7 +4557,7 @@
       </c>
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="11" t="s">
         <v>56</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -4574,7 +4574,7 @@
       </c>
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="11" t="s">
         <v>51</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -4591,7 +4591,7 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="11" t="s">
         <v>54</v>
       </c>
       <c r="B75" s="6" t="s">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AD15FB-D231-42DF-9313-A842E545EF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF266DD-E474-4C54-8C75-EA57F07FE2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2966,7 +2966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3008,6 +3008,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3472,7 +3480,7 @@
       <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="7" t="b">
+      <c r="C9" s="13" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="7" t="b">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF266DD-E474-4C54-8C75-EA57F07FE2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D13B70-F26C-4909-B557-B1CCFF1054E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="957">
   <si>
     <t>Origin Name</t>
   </si>
@@ -2902,6 +2902,9 @@
   </si>
   <si>
     <t>Fire Pea</t>
+  </si>
+  <si>
+    <t>Frost-shroom</t>
   </si>
 </sst>
 </file>
@@ -2966,7 +2969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3016,6 +3019,12 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5608,7 +5617,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -5620,8 +5629,14 @@
       <c r="E6" s="7" t="b">
         <v>1</v>
       </c>
+      <c r="F6" s="5" t="s">
+        <v>956</v>
+      </c>
       <c r="G6" s="7" t="b">
         <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -5727,7 +5742,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>103</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -5862,7 +5877,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>111</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -5906,7 +5921,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>0</v>
@@ -5947,7 +5962,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="11" t="s">
         <v>277</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -5998,7 +6013,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>109</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -6083,7 +6098,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="11" t="s">
         <v>114</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -6150,7 +6165,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="11" t="s">
         <v>123</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -6167,7 +6182,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>125</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -6180,18 +6195,18 @@
         <v>1</v>
       </c>
       <c r="G3" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>124</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C4" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7" t="b">
         <v>1</v>
@@ -6269,7 +6284,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="11" t="s">
         <v>148</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -6286,7 +6301,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="11" t="s">
         <v>149</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -6303,7 +6318,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="11" t="s">
         <v>150</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -6320,7 +6335,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>147</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -6337,7 +6352,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>151</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -6354,7 +6369,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="11" t="s">
         <v>152</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -6371,7 +6386,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="11" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -6422,7 +6437,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="11" t="s">
         <v>139</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -6439,7 +6454,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="15" t="s">
         <v>138</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -7060,7 +7075,7 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="11" t="s">
         <v>129</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -7077,7 +7092,7 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="11" t="s">
         <v>127</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -7094,7 +7109,7 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="11" t="s">
         <v>128</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -7933,7 +7948,7 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="14" t="s">
         <v>279</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -8993,7 +9008,7 @@
       </c>
     </row>
     <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="5" t="s">
+      <c r="A168" s="11" t="s">
         <v>130</v>
       </c>
       <c r="B168" s="6" t="s">
@@ -9010,7 +9025,7 @@
       </c>
     </row>
     <row r="169" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="5" t="s">
+      <c r="A169" s="11" t="s">
         <v>132</v>
       </c>
       <c r="B169" s="6" t="s">
@@ -9027,7 +9042,7 @@
       </c>
     </row>
     <row r="170" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="5" t="s">
+      <c r="A170" s="11" t="s">
         <v>131</v>
       </c>
       <c r="B170" s="6" t="s">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D13B70-F26C-4909-B557-B1CCFF1054E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6650EC9B-4EB1-4F59-B775-A6EBD8E2D1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="958">
   <si>
     <t>Origin Name</t>
   </si>
@@ -2905,6 +2905,9 @@
   </si>
   <si>
     <t>Frost-shroom</t>
+  </si>
+  <si>
+    <t>Sunflower Seeds</t>
   </si>
 </sst>
 </file>
@@ -2969,7 +2972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3019,12 +3022,6 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6454,7 +6451,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="11" t="s">
         <v>138</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -6749,7 +6746,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="11" t="s">
         <v>141</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -6766,7 +6763,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="11" t="s">
         <v>142</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -6783,7 +6780,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="11" t="s">
         <v>144</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -6800,7 +6797,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="11" t="s">
         <v>140</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -6817,7 +6814,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="11" t="s">
         <v>143</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -7948,7 +7945,7 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="14" t="s">
+      <c r="A106" s="5" t="s">
         <v>279</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -11588,7 +11585,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC464112-9E41-4E5C-8F95-91067E9A4651}">
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" style="5" customWidth="1"/>
@@ -11647,13 +11644,13 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>769</v>
+        <v>316</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>946</v>
+        <v>890</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>0</v>
@@ -11664,10 +11661,10 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>846</v>
+        <v>556</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="C4" s="7" t="b">
         <v>0</v>
@@ -11681,13 +11678,13 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>834</v>
+        <v>769</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>823</v>
+        <v>946</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>0</v>
@@ -11698,7 +11695,7 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>841</v>
@@ -11715,10 +11712,10 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -11732,10 +11729,10 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>823</v>
+        <v>841</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>0</v>
@@ -11749,13 +11746,13 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>778</v>
+        <v>819</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>782</v>
+        <v>820</v>
       </c>
       <c r="C9" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>0</v>
@@ -11766,7 +11763,7 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>877</v>
+        <v>833</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>823</v>
@@ -11783,13 +11780,13 @@
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>844</v>
+        <v>778</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>841</v>
+        <v>782</v>
       </c>
       <c r="C11" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="b">
         <v>0</v>
@@ -11800,7 +11797,7 @@
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>829</v>
+        <v>877</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>823</v>
@@ -11817,27 +11814,27 @@
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>775</v>
+        <v>844</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>776</v>
+        <v>841</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>845</v>
+        <v>936</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="C14" s="7" t="b">
         <v>0</v>
@@ -11851,7 +11848,7 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>823</v>
@@ -11868,16 +11865,16 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>836</v>
+        <v>886</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>823</v>
+        <v>890</v>
       </c>
       <c r="C16" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E16" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="7" t="b">
         <v>0</v>
@@ -11885,27 +11882,27 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>880</v>
+        <v>775</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="C17" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>822</v>
+        <v>845</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>823</v>
+        <v>841</v>
       </c>
       <c r="C18" s="7" t="b">
         <v>0</v>
@@ -11919,10 +11916,10 @@
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>785</v>
+        <v>831</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>788</v>
+        <v>823</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -11936,10 +11933,10 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>879</v>
+        <v>836</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
       <c r="C20" s="7" t="b">
         <v>0</v>
@@ -11953,10 +11950,10 @@
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>789</v>
+        <v>882</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>791</v>
+        <v>890</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>0</v>
@@ -11970,13 +11967,13 @@
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>786</v>
+        <v>880</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>788</v>
+        <v>841</v>
       </c>
       <c r="C22" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="b">
         <v>0</v>
@@ -11987,10 +11984,10 @@
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>847</v>
+        <v>822</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -12004,10 +12001,10 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>830</v>
+        <v>785</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>823</v>
+        <v>788</v>
       </c>
       <c r="C24" s="7" t="b">
         <v>0</v>
@@ -12021,10 +12018,10 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>875</v>
+        <v>914</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>823</v>
+        <v>908</v>
       </c>
       <c r="C25" s="7" t="b">
         <v>0</v>
@@ -12038,10 +12035,10 @@
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>798</v>
+        <v>933</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>793</v>
+        <v>908</v>
       </c>
       <c r="C26" s="7" t="b">
         <v>0</v>
@@ -12055,10 +12052,10 @@
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>796</v>
+        <v>910</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>793</v>
+        <v>908</v>
       </c>
       <c r="C27" s="7" t="b">
         <v>0</v>
@@ -12072,10 +12069,10 @@
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>795</v>
+        <v>912</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>793</v>
+        <v>908</v>
       </c>
       <c r="C28" s="7" t="b">
         <v>0</v>
@@ -12089,10 +12086,10 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>794</v>
+        <v>911</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>793</v>
+        <v>908</v>
       </c>
       <c r="C29" s="7" t="b">
         <v>0</v>
@@ -12106,10 +12103,10 @@
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>797</v>
+        <v>909</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>793</v>
+        <v>908</v>
       </c>
       <c r="C30" s="7" t="b">
         <v>0</v>
@@ -12123,16 +12120,19 @@
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>784</v>
+        <v>913</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>788</v>
+        <v>908</v>
       </c>
       <c r="C31" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E31" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>938</v>
       </c>
       <c r="G31" s="7" t="b">
         <v>0</v>
@@ -12140,10 +12140,10 @@
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>826</v>
+        <v>922</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>823</v>
+        <v>908</v>
       </c>
       <c r="C32" s="7" t="b">
         <v>0</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>790</v>
+        <v>879</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>791</v>
+        <v>841</v>
       </c>
       <c r="C33" s="7" t="b">
         <v>0</v>
@@ -12174,10 +12174,10 @@
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C34" s="7" t="b">
         <v>0</v>
@@ -12191,16 +12191,16 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>874</v>
+        <v>924</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>820</v>
+        <v>890</v>
       </c>
       <c r="C35" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E35" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="7" t="b">
         <v>0</v>
@@ -12208,16 +12208,16 @@
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>770</v>
+        <v>786</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>771</v>
+        <v>788</v>
       </c>
       <c r="C36" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="7" t="b">
         <v>0</v>
@@ -12225,10 +12225,10 @@
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>849</v>
+        <v>907</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>841</v>
+        <v>899</v>
       </c>
       <c r="C37" s="7" t="b">
         <v>0</v>
@@ -12242,7 +12242,7 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>841</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>878</v>
+        <v>935</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>841</v>
+        <v>916</v>
       </c>
       <c r="C39" s="7" t="b">
         <v>0</v>
@@ -12276,16 +12276,16 @@
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>837</v>
+        <v>896</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>823</v>
+        <v>900</v>
       </c>
       <c r="C40" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E40" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="7" t="b">
         <v>0</v>
@@ -12293,10 +12293,10 @@
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>853</v>
+        <v>884</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="C41" s="7" t="b">
         <v>0</v>
@@ -12310,7 +12310,7 @@
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>823</v>
@@ -12327,10 +12327,10 @@
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>781</v>
+        <v>875</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="C43" s="7" t="b">
         <v>0</v>
@@ -12344,10 +12344,10 @@
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>876</v>
+        <v>798</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>823</v>
+        <v>793</v>
       </c>
       <c r="C44" s="7" t="b">
         <v>0</v>
@@ -12361,16 +12361,16 @@
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>947</v>
+        <v>796</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>841</v>
+        <v>793</v>
       </c>
       <c r="C45" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E45" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="7" t="b">
         <v>0</v>
@@ -12378,10 +12378,10 @@
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>776</v>
+        <v>793</v>
       </c>
       <c r="C46" s="7" t="b">
         <v>0</v>
@@ -12395,10 +12395,10 @@
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="C47" s="7" t="b">
         <v>0</v>
@@ -12412,10 +12412,10 @@
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>780</v>
+        <v>797</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="C48" s="7" t="b">
         <v>0</v>
@@ -12429,10 +12429,10 @@
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>777</v>
+        <v>920</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>782</v>
+        <v>921</v>
       </c>
       <c r="C49" s="7" t="b">
         <v>0</v>
@@ -12446,10 +12446,10 @@
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="C50" s="7" t="b">
         <v>0</v>
@@ -12463,10 +12463,10 @@
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>824</v>
+        <v>918</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>823</v>
+        <v>916</v>
       </c>
       <c r="C51" s="7" t="b">
         <v>0</v>
@@ -12480,10 +12480,10 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>855</v>
+        <v>917</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>841</v>
+        <v>916</v>
       </c>
       <c r="C52" s="7" t="b">
         <v>0</v>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>854</v>
+        <v>937</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>841</v>
+        <v>916</v>
       </c>
       <c r="C53" s="7" t="b">
         <v>0</v>
@@ -12514,10 +12514,10 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>828</v>
+        <v>919</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>823</v>
+        <v>916</v>
       </c>
       <c r="C54" s="7" t="b">
         <v>0</v>
@@ -12531,7 +12531,7 @@
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>823</v>
@@ -12540,10 +12540,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>868</v>
+        <v>0</v>
       </c>
       <c r="G55" s="7" t="b">
         <v>0</v>
@@ -12551,10 +12548,10 @@
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>60</v>
+        <v>791</v>
       </c>
       <c r="C56" s="7" t="b">
         <v>0</v>
@@ -12568,10 +12565,10 @@
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>842</v>
+        <v>787</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>841</v>
+        <v>788</v>
       </c>
       <c r="C57" s="7" t="b">
         <v>0</v>
@@ -12585,10 +12582,10 @@
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>840</v>
+        <v>874</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C58" s="7" t="b">
         <v>0</v>
@@ -12602,10 +12599,10 @@
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>832</v>
+        <v>887</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>823</v>
+        <v>890</v>
       </c>
       <c r="C59" s="7" t="b">
         <v>0</v>
@@ -12619,16 +12616,16 @@
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>852</v>
+        <v>770</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>841</v>
+        <v>771</v>
       </c>
       <c r="C60" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E60" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="7" t="b">
         <v>0</v>
@@ -12636,10 +12633,10 @@
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>856</v>
+        <v>889</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>841</v>
+        <v>890</v>
       </c>
       <c r="C61" s="7" t="b">
         <v>0</v>
@@ -12653,7 +12650,7 @@
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>841</v>
@@ -12670,10 +12667,10 @@
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>823</v>
+        <v>841</v>
       </c>
       <c r="C63" s="7" t="b">
         <v>0</v>
@@ -12687,10 +12684,10 @@
     </row>
     <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>825</v>
+        <v>929</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>823</v>
+        <v>908</v>
       </c>
       <c r="C64" s="7" t="b">
         <v>0</v>
@@ -12704,10 +12701,10 @@
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>827</v>
+        <v>928</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>823</v>
+        <v>899</v>
       </c>
       <c r="C65" s="7" t="b">
         <v>0</v>
@@ -12721,10 +12718,10 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>821</v>
+        <v>930</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>820</v>
+        <v>916</v>
       </c>
       <c r="C66" s="7" t="b">
         <v>0</v>
@@ -12738,7 +12735,7 @@
     </row>
     <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>850</v>
+        <v>878</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>841</v>
@@ -12755,10 +12752,10 @@
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>556</v>
+        <v>931</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -12772,7 +12769,7 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>890</v>
@@ -12781,7 +12778,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="7" t="b">
         <v>0</v>
@@ -12789,10 +12786,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>882</v>
+        <v>903</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>0</v>
@@ -12806,10 +12803,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -12823,10 +12820,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -12840,10 +12837,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -12857,10 +12854,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -12874,10 +12871,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>909</v>
+        <v>923</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -12891,19 +12888,16 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>913</v>
+        <v>837</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>908</v>
+        <v>823</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E76" s="7" t="b">
         <v>1</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>938</v>
       </c>
       <c r="G76" s="7" t="b">
         <v>0</v>
@@ -12911,10 +12905,10 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>922</v>
+        <v>853</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>908</v>
+        <v>841</v>
       </c>
       <c r="C77" s="7" t="b">
         <v>0</v>
@@ -12928,16 +12922,16 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>924</v>
+        <v>838</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>890</v>
+        <v>823</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E78" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="7" t="b">
         <v>0</v>
@@ -12945,10 +12939,10 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>907</v>
+        <v>781</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>899</v>
+        <v>782</v>
       </c>
       <c r="C79" s="7" t="b">
         <v>0</v>
@@ -12962,10 +12956,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>896</v>
+        <v>876</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>900</v>
+        <v>823</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -12979,7 +12973,7 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>890</v>
@@ -12996,16 +12990,16 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>921</v>
+        <v>841</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E82" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="7" t="b">
         <v>0</v>
@@ -13013,10 +13007,10 @@
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>918</v>
+        <v>774</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>916</v>
+        <v>776</v>
       </c>
       <c r="C83" s="7" t="b">
         <v>0</v>
@@ -13030,10 +13024,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>916</v>
+        <v>899</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -13047,10 +13041,10 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>919</v>
+        <v>779</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>916</v>
+        <v>782</v>
       </c>
       <c r="C85" s="7" t="b">
         <v>0</v>
@@ -13064,10 +13058,10 @@
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>887</v>
+        <v>780</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>890</v>
+        <v>782</v>
       </c>
       <c r="C86" s="7" t="b">
         <v>0</v>
@@ -13081,10 +13075,10 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>889</v>
+        <v>777</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>890</v>
+        <v>782</v>
       </c>
       <c r="C87" s="7" t="b">
         <v>0</v>
@@ -13098,10 +13092,10 @@
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>885</v>
+        <v>772</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>890</v>
+        <v>773</v>
       </c>
       <c r="C88" s="7" t="b">
         <v>0</v>
@@ -13115,10 +13109,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>903</v>
+        <v>824</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>899</v>
+        <v>823</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -13132,10 +13126,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>905</v>
+        <v>855</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>899</v>
+        <v>841</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -13149,10 +13143,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>902</v>
+        <v>854</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>899</v>
+        <v>841</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -13166,10 +13160,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>904</v>
+        <v>828</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>899</v>
+        <v>823</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -13183,16 +13177,19 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>901</v>
+        <v>839</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>899</v>
+        <v>823</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E93" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>868</v>
       </c>
       <c r="G93" s="7" t="b">
         <v>0</v>
@@ -13200,10 +13197,10 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>923</v>
+        <v>792</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>899</v>
+        <v>60</v>
       </c>
       <c r="C94" s="7" t="b">
         <v>0</v>
@@ -13217,10 +13214,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>883</v>
+        <v>842</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>890</v>
+        <v>841</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -13234,10 +13231,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>906</v>
+        <v>957</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>899</v>
+        <v>823</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -13251,19 +13248,16 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>915</v>
+        <v>840</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>908</v>
+        <v>823</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E97" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>926</v>
+        <v>0</v>
       </c>
       <c r="G97" s="7" t="b">
         <v>0</v>
@@ -13271,19 +13265,16 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>895</v>
+        <v>832</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>900</v>
+        <v>823</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E98" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="G98" s="7" t="b">
         <v>0</v>
@@ -13291,10 +13282,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>897</v>
+        <v>852</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>900</v>
+        <v>841</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>0</v>
@@ -13308,10 +13299,10 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>898</v>
+        <v>856</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>900</v>
+        <v>841</v>
       </c>
       <c r="C100" s="7" t="b">
         <v>0</v>
@@ -13325,10 +13316,10 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>891</v>
+        <v>932</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="C101" s="7" t="b">
         <v>0</v>
@@ -13342,16 +13333,19 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>892</v>
+        <v>915</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="C102" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E102" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>926</v>
       </c>
       <c r="G102" s="7" t="b">
         <v>0</v>
@@ -13359,10 +13353,10 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>893</v>
+        <v>851</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>900</v>
+        <v>841</v>
       </c>
       <c r="C103" s="7" t="b">
         <v>0</v>
@@ -13376,10 +13370,10 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>894</v>
+        <v>835</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>900</v>
+        <v>823</v>
       </c>
       <c r="C104" s="7" t="b">
         <v>0</v>
@@ -13393,16 +13387,19 @@
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="C105" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E105" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>925</v>
       </c>
       <c r="G105" s="7" t="b">
         <v>0</v>
@@ -13410,7 +13407,7 @@
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>927</v>
+        <v>897</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>900</v>
@@ -13427,10 +13424,10 @@
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>928</v>
+        <v>898</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C107" s="7" t="b">
         <v>0</v>
@@ -13444,10 +13441,10 @@
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>929</v>
+        <v>891</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="C108" s="7" t="b">
         <v>0</v>
@@ -13461,10 +13458,10 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>930</v>
+        <v>892</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="C109" s="7" t="b">
         <v>0</v>
@@ -13478,7 +13475,7 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>931</v>
+        <v>893</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>900</v>
@@ -13495,10 +13492,10 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="C111" s="7" t="b">
         <v>0</v>
@@ -13512,10 +13509,10 @@
     </row>
     <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>316</v>
+        <v>894</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="C112" s="7" t="b">
         <v>0</v>
@@ -13529,10 +13526,10 @@
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
       <c r="C113" s="7" t="b">
         <v>0</v>
@@ -13546,10 +13543,10 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>934</v>
+        <v>825</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>890</v>
+        <v>823</v>
       </c>
       <c r="C114" s="7" t="b">
         <v>0</v>
@@ -13563,10 +13560,10 @@
     </row>
     <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>935</v>
+        <v>827</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>916</v>
+        <v>823</v>
       </c>
       <c r="C115" s="7" t="b">
         <v>0</v>
@@ -13580,7 +13577,7 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>936</v>
+        <v>888</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>890</v>
@@ -13597,10 +13594,10 @@
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>937</v>
+        <v>821</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>916</v>
+        <v>820</v>
       </c>
       <c r="C117" s="7" t="b">
         <v>0</v>
@@ -13612,9 +13609,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="C118" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G118" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F67">
-    <sortCondition ref="A1:A67"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G118">
+    <sortCondition ref="A1:A118"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6650EC9B-4EB1-4F59-B775-A6EBD8E2D1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CBBB3F-3EEF-4A8D-9E8A-8D8D4B41F3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20040" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -6264,7 +6264,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="11" t="s">
         <v>153</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -6661,7 +6661,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="11" t="s">
         <v>162</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -6678,7 +6678,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="11" t="s">
         <v>807</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -6695,7 +6695,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="11" t="s">
         <v>164</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -6729,7 +6729,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="11" t="s">
         <v>161</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -6916,7 +6916,7 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="11" t="s">
         <v>157</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -6933,7 +6933,7 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="11" t="s">
         <v>160</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -6950,7 +6950,7 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="11" t="s">
         <v>156</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -6967,7 +6967,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="11" t="s">
         <v>159</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -6984,7 +6984,7 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="11" t="s">
         <v>158</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -7008,7 +7008,7 @@
         <v>60</v>
       </c>
       <c r="C51" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="7" t="b">
         <v>1</v>

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CBBB3F-3EEF-4A8D-9E8A-8D8D4B41F3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F59451B-FB77-4DC9-9C06-1630FDB95C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20040" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -6213,7 +6213,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="11" t="s">
         <v>169</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -6230,7 +6230,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>167</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -6247,7 +6247,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="11" t="s">
         <v>168</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -6831,7 +6831,7 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="11" t="s">
         <v>173</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -6848,7 +6848,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="11" t="s">
         <v>174</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -6865,7 +6865,7 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="11" t="s">
         <v>170</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -6882,7 +6882,7 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="11" t="s">
         <v>171</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -6899,7 +6899,7 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="11" t="s">
         <v>172</v>
       </c>
       <c r="B45" s="6" t="s">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F59451B-FB77-4DC9-9C06-1630FDB95C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5690EC00-7029-4C9E-8D20-F86642346254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -4841,7 +4841,7 @@
       <c r="E14" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="11" t="s">
         <v>943</v>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       <c r="E15" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="11" t="s">
         <v>944</v>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       <c r="E16" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="11" t="s">
         <v>945</v>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       <c r="E18" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="11" t="s">
         <v>954</v>
       </c>
     </row>
@@ -6485,7 +6485,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="11" t="s">
         <v>200</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -7395,7 +7395,7 @@
       </c>
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="11" t="s">
         <v>183</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -7429,7 +7429,7 @@
       </c>
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="11" t="s">
         <v>192</v>
       </c>
       <c r="B76" s="6" t="s">
@@ -7446,7 +7446,7 @@
       </c>
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="11" t="s">
         <v>184</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -8662,7 +8662,7 @@
       </c>
     </row>
     <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="11" t="s">
         <v>230</v>
       </c>
       <c r="B148" s="6" t="s">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5690EC00-7029-4C9E-8D20-F86642346254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193158CB-FD3F-4721-A004-BACF37073620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20025" yWindow="-21600" windowWidth="17415" windowHeight="20985" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -6400,7 +6400,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="11" t="s">
         <v>135</v>
       </c>
       <c r="B16" s="6" t="s">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193158CB-FD3F-4721-A004-BACF37073620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C989C5-A2F5-47DF-9B79-D6B195853999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="7965" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -2914,7 +2914,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2932,6 +2932,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Trebuchet MS"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
       <name val="Trebuchet MS"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2972,7 +2979,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3022,6 +3029,9 @@
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3497,7 +3507,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -4007,7 +4017,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="11" t="s">
         <v>21</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -4041,7 +4051,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -4075,7 +4085,7 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -4143,7 +4153,7 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -4194,7 +4204,7 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="14" t="s">
         <v>63</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -4364,7 +4374,7 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -5546,7 +5556,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="14" t="s">
         <v>105</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -5563,7 +5573,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="14" t="s">
         <v>100</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -5580,7 +5590,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="14" t="s">
         <v>101</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -5597,7 +5607,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="14" t="s">
         <v>104</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -5637,7 +5647,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="14" t="s">
         <v>89</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -5654,7 +5664,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="14" t="s">
         <v>93</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -5671,7 +5681,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="14" t="s">
         <v>94</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -5688,7 +5698,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="14" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -5705,7 +5715,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="14" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -5722,7 +5732,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -5756,7 +5766,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="14" t="s">
         <v>102</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -5773,7 +5783,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="14" t="s">
         <v>90</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -5908,7 +5918,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="14" t="s">
         <v>115</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -5925,7 +5935,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="14" t="s">
         <v>108</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -5942,7 +5952,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="14" t="s">
         <v>119</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -5976,7 +5986,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="14" t="s">
         <v>116</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -5993,7 +6003,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="14" t="s">
         <v>120</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -6027,7 +6037,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="14" t="s">
         <v>107</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -6044,7 +6054,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="14" t="s">
         <v>118</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -6061,7 +6071,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="14" t="s">
         <v>110</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -6078,7 +6088,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="14" t="s">
         <v>121</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -6468,7 +6478,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="11" t="s">
         <v>204</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -6508,7 +6518,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="11" t="s">
         <v>196</v>
       </c>
       <c r="B22" s="6" t="s">

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C989C5-A2F5-47DF-9B79-D6B195853999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32FC86D-5256-4ED1-9808-3C26E6C37467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="7965" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="958">
   <si>
     <t>Origin Name</t>
   </si>
@@ -2481,9 +2481,6 @@
     <t>Jolly Bishop</t>
   </si>
   <si>
-    <t>Missile Queen</t>
-  </si>
-  <si>
     <t>Holly Rook</t>
   </si>
   <si>
@@ -2908,6 +2905,9 @@
   </si>
   <si>
     <t>Sunflower Seeds</t>
+  </si>
+  <si>
+    <t>Missile Toe Queen</t>
   </si>
 </sst>
 </file>
@@ -3364,7 +3364,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -3517,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7" t="b">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4734,7 +4734,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -4793,7 +4793,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E10" s="7" t="b">
         <v>0</v>
@@ -4807,7 +4807,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E11" s="7" t="b">
         <v>0</v>
@@ -4821,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E12" s="7" t="b">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4866,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4880,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4894,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4908,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -5549,7 +5549,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -5637,13 +5637,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -5843,7 +5843,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -6165,7 +6165,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -6508,13 +6508,13 @@
         <v>1</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G21" s="7" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -6535,7 +6535,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="11" t="s">
         <v>195</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -6552,7 +6552,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="11" t="s">
         <v>199</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -6569,7 +6569,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="14" t="s">
         <v>203</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -6586,7 +6586,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="11" t="s">
         <v>201</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -6603,7 +6603,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="11" t="s">
         <v>194</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -6620,7 +6620,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="11" t="s">
         <v>198</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -6633,11 +6633,11 @@
         <v>1</v>
       </c>
       <c r="G28" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="11" t="s">
         <v>202</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -6654,7 +6654,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="11" t="s">
         <v>197</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>159</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
         <v>158</v>
       </c>
@@ -7010,8 +7010,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
         <v>802</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -7027,11 +7027,14 @@
         <v>804</v>
       </c>
       <c r="G51" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
         <v>302</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -7047,8 +7050,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="14" t="s">
         <v>303</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -7064,9 +7067,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>881</v>
+    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>880</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>60</v>
@@ -7081,7 +7084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>129</v>
       </c>
@@ -7098,7 +7101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>127</v>
       </c>
@@ -7115,7 +7118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>128</v>
       </c>
@@ -7132,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>212</v>
       </c>
@@ -7149,7 +7152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>219</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>216</v>
       </c>
@@ -7183,7 +7186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>211</v>
       </c>
@@ -7200,7 +7203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>217</v>
       </c>
@@ -7217,7 +7220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>214</v>
       </c>
@@ -7234,7 +7237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>213</v>
       </c>
@@ -7251,7 +7254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>215</v>
       </c>
@@ -7268,7 +7271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>209</v>
       </c>
@@ -7285,7 +7288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>206</v>
       </c>
@@ -7302,7 +7305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>207</v>
       </c>
@@ -7319,7 +7322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>210</v>
       </c>
@@ -7336,7 +7339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>218</v>
       </c>
@@ -7353,7 +7356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>208</v>
       </c>
@@ -7370,8 +7373,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
         <v>187</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -7387,8 +7390,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11" t="s">
         <v>191</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -7404,7 +7407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
         <v>183</v>
       </c>
@@ -7421,8 +7424,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
+    <row r="75" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
         <v>180</v>
       </c>
       <c r="B75" s="6" t="s">
@@ -7438,7 +7441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
         <v>192</v>
       </c>
@@ -7455,7 +7458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
         <v>184</v>
       </c>
@@ -7472,8 +7475,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="s">
+    <row r="78" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="11" t="s">
         <v>185</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -7483,14 +7486,14 @@
         <v>1</v>
       </c>
       <c r="E78" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="s">
+    <row r="79" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="11" t="s">
         <v>182</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -7506,8 +7509,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="5" t="s">
+    <row r="80" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="11" t="s">
         <v>193</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -7523,7 +7526,10 @@
         <v>803</v>
       </c>
       <c r="G80" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7557,7 +7563,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>815</v>
+        <v>957</v>
       </c>
       <c r="G82" s="7" t="b">
         <v>0</v>
@@ -8979,7 +8985,7 @@
     </row>
     <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>221</v>
@@ -8996,7 +9002,7 @@
     </row>
     <row r="167" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>221</v>
@@ -9008,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G167" s="7" t="b">
         <v>0</v>
@@ -9109,7 +9115,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -9265,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G10" s="7" t="b">
         <v>1</v>
@@ -9574,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G28" s="7" t="b">
         <v>0</v>
@@ -10053,7 +10059,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G56" s="7" t="b">
         <v>0</v>
@@ -10214,7 +10220,7 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>361</v>
@@ -10401,7 +10407,7 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>361</v>
@@ -10413,7 +10419,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G77" s="7" t="b">
         <v>0</v>
@@ -10813,7 +10819,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G100" s="7" t="b">
         <v>0</v>
@@ -10974,7 +10980,7 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>437</v>
@@ -11079,7 +11085,7 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>437</v>
@@ -11162,7 +11168,7 @@
         <v>1</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G120" s="7" t="b">
         <v>0</v>
@@ -11199,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G122" s="7" t="b">
         <v>0</v>
@@ -11219,7 +11225,7 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G123" s="7" t="b">
         <v>0</v>
@@ -11307,7 +11313,7 @@
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G128" s="7" t="b">
         <v>0</v>
@@ -11536,7 +11542,7 @@
     </row>
     <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>353</v>
@@ -11629,7 +11635,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -11657,7 +11663,7 @@
         <v>316</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C3" s="7" t="b">
         <v>0</v>
@@ -11674,7 +11680,7 @@
         <v>556</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C4" s="7" t="b">
         <v>0</v>
@@ -11691,7 +11697,7 @@
         <v>769</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C5" s="7" t="b">
         <v>1</v>
@@ -11705,10 +11711,10 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -11722,10 +11728,10 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -11739,10 +11745,10 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>0</v>
@@ -11756,10 +11762,10 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>819</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>820</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -11773,10 +11779,10 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -11807,10 +11813,10 @@
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C12" s="7" t="b">
         <v>0</v>
@@ -11824,10 +11830,10 @@
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C13" s="7" t="b">
         <v>0</v>
@@ -11841,10 +11847,10 @@
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C14" s="7" t="b">
         <v>0</v>
@@ -11858,10 +11864,10 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C15" s="7" t="b">
         <v>0</v>
@@ -11875,10 +11881,10 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C16" s="7" t="b">
         <v>0</v>
@@ -11909,10 +11915,10 @@
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C18" s="7" t="b">
         <v>0</v>
@@ -11926,10 +11932,10 @@
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -11943,10 +11949,10 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C20" s="7" t="b">
         <v>0</v>
@@ -11960,10 +11966,10 @@
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>0</v>
@@ -11977,10 +11983,10 @@
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C22" s="7" t="b">
         <v>0</v>
@@ -11994,10 +12000,10 @@
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>822</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>823</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -12028,10 +12034,10 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C25" s="7" t="b">
         <v>0</v>
@@ -12045,10 +12051,10 @@
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C26" s="7" t="b">
         <v>0</v>
@@ -12062,10 +12068,10 @@
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C27" s="7" t="b">
         <v>0</v>
@@ -12079,10 +12085,10 @@
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C28" s="7" t="b">
         <v>0</v>
@@ -12096,10 +12102,10 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C29" s="7" t="b">
         <v>0</v>
@@ -12113,10 +12119,10 @@
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C30" s="7" t="b">
         <v>0</v>
@@ -12130,10 +12136,10 @@
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C31" s="7" t="b">
         <v>0</v>
@@ -12142,7 +12148,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G31" s="7" t="b">
         <v>0</v>
@@ -12150,10 +12156,10 @@
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C32" s="7" t="b">
         <v>0</v>
@@ -12167,10 +12173,10 @@
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C33" s="7" t="b">
         <v>0</v>
@@ -12201,10 +12207,10 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C35" s="7" t="b">
         <v>0</v>
@@ -12235,10 +12241,10 @@
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C37" s="7" t="b">
         <v>0</v>
@@ -12252,10 +12258,10 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C38" s="7" t="b">
         <v>0</v>
@@ -12269,10 +12275,10 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C39" s="7" t="b">
         <v>0</v>
@@ -12286,10 +12292,10 @@
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C40" s="7" t="b">
         <v>0</v>
@@ -12303,10 +12309,10 @@
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C41" s="7" t="b">
         <v>0</v>
@@ -12320,10 +12326,10 @@
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C42" s="7" t="b">
         <v>0</v>
@@ -12337,10 +12343,10 @@
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C43" s="7" t="b">
         <v>0</v>
@@ -12439,10 +12445,10 @@
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>920</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>921</v>
       </c>
       <c r="C49" s="7" t="b">
         <v>0</v>
@@ -12473,10 +12479,10 @@
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C51" s="7" t="b">
         <v>0</v>
@@ -12490,10 +12496,10 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C52" s="7" t="b">
         <v>0</v>
@@ -12507,10 +12513,10 @@
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C53" s="7" t="b">
         <v>0</v>
@@ -12524,10 +12530,10 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C54" s="7" t="b">
         <v>0</v>
@@ -12541,10 +12547,10 @@
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C55" s="7" t="b">
         <v>0</v>
@@ -12592,10 +12598,10 @@
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C58" s="7" t="b">
         <v>0</v>
@@ -12609,10 +12615,10 @@
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C59" s="7" t="b">
         <v>0</v>
@@ -12643,10 +12649,10 @@
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>889</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>890</v>
       </c>
       <c r="C61" s="7" t="b">
         <v>0</v>
@@ -12660,10 +12666,10 @@
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C62" s="7" t="b">
         <v>0</v>
@@ -12677,10 +12683,10 @@
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C63" s="7" t="b">
         <v>0</v>
@@ -12694,10 +12700,10 @@
     </row>
     <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C64" s="7" t="b">
         <v>0</v>
@@ -12711,10 +12717,10 @@
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C65" s="7" t="b">
         <v>0</v>
@@ -12728,10 +12734,10 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C66" s="7" t="b">
         <v>0</v>
@@ -12745,10 +12751,10 @@
     </row>
     <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C67" s="7" t="b">
         <v>0</v>
@@ -12762,10 +12768,10 @@
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -12779,10 +12785,10 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C69" s="7" t="b">
         <v>0</v>
@@ -12796,10 +12802,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>0</v>
@@ -12813,10 +12819,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -12830,10 +12836,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -12847,10 +12853,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -12864,10 +12870,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -12881,10 +12887,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -12898,10 +12904,10 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
@@ -12915,10 +12921,10 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C77" s="7" t="b">
         <v>0</v>
@@ -12932,10 +12938,10 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
@@ -12966,10 +12972,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -12983,10 +12989,10 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C81" s="7" t="b">
         <v>0</v>
@@ -13000,10 +13006,10 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>0</v>
@@ -13034,10 +13040,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -13119,10 +13125,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -13136,10 +13142,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -13153,10 +13159,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -13170,10 +13176,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -13187,10 +13193,10 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
@@ -13199,7 +13205,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G93" s="7" t="b">
         <v>0</v>
@@ -13224,10 +13230,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -13241,10 +13247,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -13258,10 +13264,10 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>0</v>
@@ -13275,10 +13281,10 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>0</v>
@@ -13292,10 +13298,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>0</v>
@@ -13309,10 +13315,10 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C100" s="7" t="b">
         <v>0</v>
@@ -13326,10 +13332,10 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C101" s="7" t="b">
         <v>0</v>
@@ -13343,10 +13349,10 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C102" s="7" t="b">
         <v>0</v>
@@ -13355,7 +13361,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G102" s="7" t="b">
         <v>0</v>
@@ -13363,10 +13369,10 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C103" s="7" t="b">
         <v>0</v>
@@ -13380,10 +13386,10 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C104" s="7" t="b">
         <v>0</v>
@@ -13397,10 +13403,10 @@
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C105" s="7" t="b">
         <v>0</v>
@@ -13409,7 +13415,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G105" s="7" t="b">
         <v>0</v>
@@ -13417,10 +13423,10 @@
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C106" s="7" t="b">
         <v>0</v>
@@ -13434,10 +13440,10 @@
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C107" s="7" t="b">
         <v>0</v>
@@ -13451,10 +13457,10 @@
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C108" s="7" t="b">
         <v>0</v>
@@ -13468,10 +13474,10 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C109" s="7" t="b">
         <v>0</v>
@@ -13485,10 +13491,10 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C110" s="7" t="b">
         <v>0</v>
@@ -13502,10 +13508,10 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C111" s="7" t="b">
         <v>0</v>
@@ -13519,10 +13525,10 @@
     </row>
     <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C112" s="7" t="b">
         <v>0</v>
@@ -13536,10 +13542,10 @@
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C113" s="7" t="b">
         <v>0</v>
@@ -13553,10 +13559,10 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C114" s="7" t="b">
         <v>0</v>
@@ -13570,10 +13576,10 @@
     </row>
     <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C115" s="7" t="b">
         <v>0</v>
@@ -13587,10 +13593,10 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C116" s="7" t="b">
         <v>0</v>
@@ -13604,10 +13610,10 @@
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C117" s="7" t="b">
         <v>0</v>
@@ -13621,10 +13627,10 @@
     </row>
     <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C118" s="7" t="b">
         <v>0</v>
@@ -13681,7 +13687,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -14546,7 +14552,7 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>582</v>
@@ -14605,7 +14611,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -16327,7 +16333,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -16361,7 +16367,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="7" t="b">
         <v>0</v>
@@ -17083,7 +17089,7 @@
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>638</v>
@@ -17098,7 +17104,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -17336,7 +17342,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G60" s="7" t="b">
         <v>0</v>
@@ -19099,7 +19105,7 @@
     </row>
     <row r="164" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>638</v>

--- a/plant_port_checklist.xlsx
+++ b/plant_port_checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_rogue_garden_wiki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32FC86D-5256-4ED1-9808-3C26E6C37467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC315414-AB7D-47C9-8C4A-6C0CF58003EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="958">
   <si>
     <t>Origin Name</t>
   </si>
@@ -852,9 +852,6 @@
     <t>Rhubarbarian</t>
   </si>
   <si>
-    <t>Mega Gatling Pea</t>
-  </si>
-  <si>
     <t>Levitater</t>
   </si>
   <si>
@@ -2908,6 +2905,9 @@
   </si>
   <si>
     <t>Missile Toe Queen</t>
+  </si>
+  <si>
+    <t>Buzz Button</t>
   </si>
 </sst>
 </file>
@@ -2944,7 +2944,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2954,6 +2954,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2979,7 +2985,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3031,6 +3037,9 @@
       </extLst>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3364,7 +3373,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -4667,7 +4676,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -4678,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C2" s="7" t="b">
         <v>1</v>
@@ -4692,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C3" s="7" t="b">
         <v>0</v>
@@ -4706,7 +4715,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C4" s="7" t="b">
         <v>0</v>
@@ -4720,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C5" s="7" t="b">
         <v>1</v>
@@ -4734,7 +4743,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -4751,7 +4760,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E7" s="7" t="b">
         <v>0</v>
@@ -4765,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>0</v>
@@ -4779,7 +4788,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>0</v>
@@ -4793,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E10" s="7" t="b">
         <v>0</v>
@@ -4807,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E11" s="7" t="b">
         <v>0</v>
@@ -4821,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E12" s="7" t="b">
         <v>0</v>
@@ -4835,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>0</v>
@@ -4852,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4866,7 +4875,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4880,7 +4889,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4894,7 +4903,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -4908,7 +4917,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -5549,7 +5558,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -5637,13 +5646,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -5843,7 +5852,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -5970,7 +5979,7 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>113</v>
@@ -6131,7 +6140,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A72B5E-30F7-44EA-9A7D-62AB51A3920C}">
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" style="5" customWidth="1"/>
@@ -6165,7 +6174,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -6508,13 +6517,13 @@
         <v>1</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G21" s="7" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -6689,7 +6698,7 @@
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>166</v>
@@ -6905,7 +6914,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -7012,7 +7021,7 @@
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>60</v>
@@ -7024,18 +7033,18 @@
         <v>1</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G51" s="7" t="b">
         <v>1</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>60</v>
@@ -7052,7 +7061,7 @@
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>60</v>
@@ -7069,7 +7078,7 @@
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>60</v>
@@ -7523,17 +7532,17 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G80" s="7" t="b">
         <v>1</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="11" t="s">
         <v>181</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -7550,7 +7559,7 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="11" t="s">
         <v>190</v>
       </c>
       <c r="B82" s="6" t="s">
@@ -7563,14 +7572,14 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G82" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="11" t="s">
         <v>189</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -7587,7 +7596,7 @@
       </c>
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="14" t="s">
         <v>177</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -7597,14 +7606,14 @@
         <v>0</v>
       </c>
       <c r="E84" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="11" t="s">
         <v>179</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -7621,7 +7630,7 @@
       </c>
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="11" t="s">
         <v>178</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -7638,7 +7647,7 @@
       </c>
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="11" t="s">
         <v>186</v>
       </c>
       <c r="B87" s="6" t="s">
@@ -7651,11 +7660,11 @@
         <v>1</v>
       </c>
       <c r="G87" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="11" t="s">
         <v>188</v>
       </c>
       <c r="B88" s="6" t="s">
@@ -7672,7 +7681,7 @@
       </c>
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="11" t="s">
         <v>226</v>
       </c>
       <c r="B89" s="6" t="s">
@@ -7689,8 +7698,8 @@
       </c>
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
-        <v>292</v>
+      <c r="A90" s="14" t="s">
+        <v>291</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>221</v>
@@ -7706,8 +7715,8 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
-        <v>283</v>
+      <c r="A91" s="11" t="s">
+        <v>282</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>221</v>
@@ -7723,8 +7732,8 @@
       </c>
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>285</v>
+      <c r="A92" s="14" t="s">
+        <v>284</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>221</v>
@@ -7740,8 +7749,8 @@
       </c>
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>294</v>
+      <c r="A93" s="14" t="s">
+        <v>293</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>221</v>
@@ -7757,7 +7766,7 @@
       </c>
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="11" t="s">
         <v>237</v>
       </c>
       <c r="B94" s="6" t="s">
@@ -7774,8 +7783,8 @@
       </c>
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
-        <v>295</v>
+      <c r="A95" s="14" t="s">
+        <v>294</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>221</v>
@@ -7791,7 +7800,7 @@
       </c>
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
+      <c r="A96" s="14" t="s">
         <v>268</v>
       </c>
       <c r="B96" s="6" t="s">
@@ -7808,7 +7817,7 @@
       </c>
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="5" t="s">
+      <c r="A97" s="11" t="s">
         <v>224</v>
       </c>
       <c r="B97" s="6" t="s">
@@ -7825,7 +7834,7 @@
       </c>
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
+      <c r="A98" s="14" t="s">
         <v>253</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -7842,7 +7851,7 @@
       </c>
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
+      <c r="A99" s="15" t="s">
         <v>227</v>
       </c>
       <c r="B99" s="6" t="s">
@@ -7852,14 +7861,14 @@
         <v>0</v>
       </c>
       <c r="E99" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
+      <c r="A100" s="14" t="s">
         <v>259</v>
       </c>
       <c r="B100" s="6" t="s">
@@ -7876,8 +7885,8 @@
       </c>
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
-        <v>280</v>
+      <c r="A101" s="14" t="s">
+        <v>279</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>221</v>
@@ -7893,7 +7902,7 @@
       </c>
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
+      <c r="A102" s="14" t="s">
         <v>270</v>
       </c>
       <c r="B102" s="6" t="s">
@@ -7910,8 +7919,8 @@
       </c>
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>288</v>
+      <c r="A103" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>221</v>
@@ -7927,8 +7936,8 @@
       </c>
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="5" t="s">
-        <v>278</v>
+      <c r="A104" s="14" t="s">
+        <v>277</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>221</v>
@@ -7944,7 +7953,7 @@
       </c>
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="5" t="s">
+      <c r="A105" s="11" t="s">
         <v>269</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -7961,8 +7970,8 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="5" t="s">
-        <v>279</v>
+      <c r="A106" s="11" t="s">
+        <v>278</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>221</v>
@@ -7973,13 +7982,16 @@
       <c r="E106" s="7" t="b">
         <v>1</v>
       </c>
+      <c r="F106" s="5" t="s">
+        <v>957</v>
+      </c>
       <c r="G106" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="5" t="s">
-        <v>300</v>
+      <c r="A107" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>221</v>
@@ -7995,8 +8007,8 @@
       </c>
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="5" t="s">
-        <v>287</v>
+      <c r="A108" s="14" t="s">
+        <v>286</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>221</v>
@@ -8012,7 +8024,7 @@
       </c>
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="5" t="s">
+      <c r="A109" s="11" t="s">
         <v>222</v>
       </c>
       <c r="B109" s="6" t="s">
@@ -8032,7 +8044,7 @@
       </c>
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="11" t="s">
         <v>242</v>
       </c>
       <c r="B110" s="6" t="s">
@@ -8049,7 +8061,7 @@
       </c>
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="5" t="s">
+      <c r="A111" s="11" t="s">
         <v>235</v>
       </c>
       <c r="B111" s="6" t="s">
@@ -8066,7 +8078,7 @@
       </c>
     </row>
     <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="5" t="s">
+      <c r="A112" s="11" t="s">
         <v>257</v>
       </c>
       <c r="B112" s="6" t="s">
@@ -8083,8 +8095,8 @@
       </c>
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="5" t="s">
-        <v>289</v>
+      <c r="A113" s="11" t="s">
+        <v>288</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>221</v>
@@ -8100,8 +8112,8 @@
       </c>
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
-        <v>290</v>
+      <c r="A114" s="14" t="s">
+        <v>289</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>221</v>
@@ -8168,8 +8180,8 @@
       </c>
     </row>
     <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="5" t="s">
-        <v>296</v>
+      <c r="A118" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>221</v>
@@ -8219,8 +8231,8 @@
       </c>
     </row>
     <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="5" t="s">
-        <v>291</v>
+      <c r="A121" s="14" t="s">
+        <v>290</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>221</v>
@@ -8236,7 +8248,7 @@
       </c>
     </row>
     <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="14" t="s">
         <v>244</v>
       </c>
       <c r="B122" s="6" t="s">
@@ -8253,8 +8265,8 @@
       </c>
     </row>
     <row r="123" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="5" t="s">
-        <v>299</v>
+      <c r="A123" s="14" t="s">
+        <v>298</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>221</v>
@@ -8287,7 +8299,7 @@
       </c>
     </row>
     <row r="125" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="5" t="s">
+      <c r="A125" s="14" t="s">
         <v>264</v>
       </c>
       <c r="B125" s="6" t="s">
@@ -8372,7 +8384,7 @@
       </c>
     </row>
     <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="5" t="s">
+      <c r="A130" s="14" t="s">
         <v>239</v>
       </c>
       <c r="B130" s="6" t="s">
@@ -8407,7 +8419,7 @@
     </row>
     <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>221</v>
@@ -8423,8 +8435,8 @@
       </c>
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="5" t="s">
-        <v>293</v>
+      <c r="A133" s="14" t="s">
+        <v>292</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>221</v>
@@ -8440,8 +8452,8 @@
       </c>
     </row>
     <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="5" t="s">
-        <v>281</v>
+      <c r="A134" s="14" t="s">
+        <v>280</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>221</v>
@@ -8458,7 +8470,7 @@
     </row>
     <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>221</v>
@@ -8467,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="7" t="b">
         <v>0</v>
@@ -8475,7 +8487,7 @@
     </row>
     <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>221</v>
@@ -8487,12 +8499,12 @@
         <v>1</v>
       </c>
       <c r="G136" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>221</v>
@@ -8509,30 +8521,30 @@
     </row>
     <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C138" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="7" t="b">
         <v>1</v>
       </c>
       <c r="G138" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C139" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" s="7" t="b">
         <v>1</v>
@@ -8542,8 +8554,8 @@
       </c>
     </row>
     <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="5" t="s">
-        <v>258</v>
+      <c r="A140" s="14" t="s">
+        <v>238</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>221</v>
@@ -8552,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" s="7" t="b">
         <v>0</v>
@@ -8560,16 +8572,16 @@
     </row>
     <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C141" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" s="7" t="b">
         <v>0</v>
@@ -8577,7 +8589,7 @@
     </row>
     <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>221</v>
@@ -8586,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="E142" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" s="7" t="b">
         <v>0</v>
@@ -8594,7 +8606,7 @@
     </row>
     <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>221</v>
@@ -8603,32 +8615,32 @@
         <v>1</v>
       </c>
       <c r="E143" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="5" t="s">
-        <v>240</v>
+      <c r="A144" s="14" t="s">
+        <v>271</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C144" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="5" t="s">
-        <v>271</v>
+      <c r="A145" s="14" t="s">
+        <v>281</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>221</v>
@@ -8644,8 +8656,8 @@
       </c>
     </row>
     <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="5" t="s">
-        <v>282</v>
+      <c r="A146" s="14" t="s">
+        <v>300</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>221</v>
@@ -8661,25 +8673,25 @@
       </c>
     </row>
     <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="5" t="s">
-        <v>301</v>
+      <c r="A147" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C147" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="11" t="s">
-        <v>230</v>
+      <c r="A148" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>221</v>
@@ -8691,12 +8703,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>221</v>
@@ -8708,12 +8720,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>221</v>
@@ -8730,33 +8742,33 @@
     </row>
     <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C151" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="7" t="b">
         <v>1</v>
       </c>
       <c r="G151" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C152" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" s="7" t="b">
         <v>0</v>
@@ -8764,24 +8776,24 @@
     </row>
     <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>221</v>
       </c>
       <c r="C153" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="5" t="s">
-        <v>254</v>
+      <c r="A154" s="14" t="s">
+        <v>283</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>221</v>
@@ -8790,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="E154" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" s="7" t="b">
         <v>0</v>
@@ -8798,7 +8810,7 @@
     </row>
     <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>221</v>
@@ -8807,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="E155" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" s="7" t="b">
         <v>0</v>
@@ -8815,7 +8827,7 @@
     </row>
     <row r="156" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>221</v>
@@ -8831,8 +8843,8 @@
       </c>
     </row>
     <row r="157" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="5" t="s">
-        <v>267</v>
+      <c r="A157" s="14" t="s">
+        <v>266</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>221</v>
@@ -8841,15 +8853,15 @@
         <v>0</v>
       </c>
       <c r="E157" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G157" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="5" t="s">
-        <v>266</v>
+      <c r="A158" s="14" t="s">
+        <v>273</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>221</v>
@@ -8866,7 +8878,7 @@
     </row>
     <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>221</v>
@@ -8875,15 +8887,15 @@
         <v>0</v>
       </c>
       <c r="E159" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="5" t="s">
-        <v>246</v>
+      <c r="A160" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>221</v>
@@ -8892,15 +8904,15 @@
         <v>0</v>
       </c>
       <c r="E160" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="5" t="s">
-        <v>251</v>
+      <c r="A161" s="14" t="s">
+        <v>243</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>221</v>
@@ -8917,7 +8929,7 @@
     </row>
     <row r="162" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>221</v>
@@ -8926,15 +8938,15 @@
         <v>0</v>
       </c>
       <c r="E162" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="5" t="s">
-        <v>275</v>
+      <c r="A163" s="14" t="s">
+        <v>296</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>221</v>
@@ -8943,15 +8955,15 @@
         <v>0</v>
       </c>
       <c r="E163" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="5" t="s">
-        <v>297</v>
+      <c r="A164" s="14" t="s">
+        <v>234</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>221</v>
@@ -8967,8 +8979,8 @@
       </c>
     </row>
     <row r="165" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="5" t="s">
-        <v>234</v>
+      <c r="A165" s="14" t="s">
+        <v>937</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>221</v>
@@ -8994,27 +9006,27 @@
         <v>0</v>
       </c>
       <c r="E166" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>939</v>
       </c>
       <c r="G166" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="5" t="s">
-        <v>939</v>
+      <c r="A167" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="C167" s="7" t="b">
         <v>0</v>
       </c>
       <c r="E167" s="7" t="b">
         <v>1</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>940</v>
       </c>
       <c r="G167" s="7" t="b">
         <v>0</v>
@@ -9022,13 +9034,13 @@
     </row>
     <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>134</v>
       </c>
       <c r="C168" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" s="7" t="b">
         <v>1</v>
@@ -9039,7 +9051,7 @@
     </row>
     <row r="169" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>134</v>
@@ -9051,29 +9063,12 @@
         <v>1</v>
       </c>
       <c r="G169" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C170" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E170" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G170" s="7" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F170">
-    <sortCondition ref="B2:B170"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F169">
+    <sortCondition ref="B2:B169"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9115,7 +9110,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -9123,7 +9118,7 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>175</v>
@@ -9140,7 +9135,7 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>175</v>
@@ -9157,7 +9152,7 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>155</v>
@@ -9174,7 +9169,7 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>155</v>
@@ -9191,7 +9186,7 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>155</v>
@@ -9208,10 +9203,10 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -9225,10 +9220,10 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>0</v>
@@ -9242,10 +9237,10 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -9259,10 +9254,10 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -9271,7 +9266,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G10" s="7" t="b">
         <v>1</v>
@@ -9279,10 +9274,10 @@
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C11" s="7" t="b">
         <v>0</v>
@@ -9296,10 +9291,10 @@
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C12" s="7" t="b">
         <v>0</v>
@@ -9313,7 +9308,7 @@
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>154</v>
@@ -9330,7 +9325,7 @@
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>154</v>
@@ -9347,7 +9342,7 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>154</v>
@@ -9364,7 +9359,7 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>145</v>
@@ -9381,7 +9376,7 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>145</v>
@@ -9398,10 +9393,10 @@
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C18" s="7" t="b">
         <v>0</v>
@@ -9415,10 +9410,10 @@
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -9432,10 +9427,10 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C20" s="7" t="b">
         <v>0</v>
@@ -9449,10 +9444,10 @@
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>0</v>
@@ -9466,10 +9461,10 @@
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C22" s="7" t="b">
         <v>0</v>
@@ -9483,10 +9478,10 @@
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -9500,7 +9495,7 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>166</v>
@@ -9517,7 +9512,7 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>166</v>
@@ -9534,7 +9529,7 @@
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>166</v>
@@ -9551,7 +9546,7 @@
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>166</v>
@@ -9571,7 +9566,7 @@
         <v>111</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C28" s="7" t="b">
         <v>0</v>
@@ -9580,7 +9575,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G28" s="7" t="b">
         <v>0</v>
@@ -9588,10 +9583,10 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C29" s="7" t="b">
         <v>0</v>
@@ -9605,10 +9600,10 @@
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="C30" s="7" t="b">
         <v>0</v>
@@ -9622,10 +9617,10 @@
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C31" s="7" t="b">
         <v>0</v>
@@ -9639,7 +9634,7 @@
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>146</v>
@@ -9656,7 +9651,7 @@
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>146</v>
@@ -9673,10 +9668,10 @@
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C34" s="7" t="b">
         <v>0</v>
@@ -9690,10 +9685,10 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C35" s="7" t="b">
         <v>0</v>
@@ -9707,10 +9702,10 @@
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C36" s="7" t="b">
         <v>0</v>
@@ -9724,10 +9719,10 @@
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C37" s="7" t="b">
         <v>0</v>
@@ -9741,10 +9736,10 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C38" s="7" t="b">
         <v>0</v>
@@ -9758,10 +9753,10 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C39" s="7" t="b">
         <v>0</v>
@@ -9775,10 +9770,10 @@
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C40" s="7" t="b">
         <v>0</v>
@@ -9792,10 +9787,10 @@
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C41" s="7" t="b">
         <v>0</v>
@@ -9809,10 +9804,10 @@
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C42" s="7" t="b">
         <v>0</v>
@@ -9826,10 +9821,10 @@
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C43" s="7" t="b">
         <v>0</v>
@@ -9843,10 +9838,10 @@
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C44" s="7" t="b">
         <v>0</v>
@@ -9860,10 +9855,10 @@
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C45" s="7" t="b">
         <v>0</v>
@@ -9877,10 +9872,10 @@
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C46" s="7" t="b">
         <v>0</v>
@@ -9894,10 +9889,10 @@
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C47" s="7" t="b">
         <v>0</v>
@@ -9911,10 +9906,10 @@
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C48" s="7" t="b">
         <v>0</v>
@@ -9928,10 +9923,10 @@
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C49" s="7" t="b">
         <v>0</v>
@@ -9945,10 +9940,10 @@
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C50" s="7" t="b">
         <v>0</v>
@@ -9962,10 +9957,10 @@
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C51" s="7" t="b">
         <v>0</v>
@@ -9979,10 +9974,10 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C52" s="7" t="b">
         <v>0</v>
@@ -9996,10 +9991,10 @@
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" s="7" t="b">
         <v>0</v>
@@ -10013,10 +10008,10 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C54" s="7" t="b">
         <v>0</v>
@@ -10030,10 +10025,10 @@
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C55" s="7" t="b">
         <v>0</v>
@@ -10047,10 +10042,10 @@
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C56" s="7" t="b">
         <v>0</v>
@@ -10059,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G56" s="7" t="b">
         <v>0</v>
@@ -10067,10 +10062,10 @@
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C57" s="7" t="b">
         <v>0</v>
@@ -10084,10 +10079,10 @@
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C58" s="7" t="b">
         <v>0</v>
@@ -10101,10 +10096,10 @@
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C59" s="7" t="b">
         <v>0</v>
@@ -10118,10 +10113,10 @@
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C60" s="7" t="b">
         <v>0</v>
@@ -10135,10 +10130,10 @@
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C61" s="7" t="b">
         <v>0</v>
@@ -10152,10 +10147,10 @@
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="7" t="b">
         <v>0</v>
@@ -10169,10 +10164,10 @@
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C63" s="7" t="b">
         <v>0</v>
@@ -10186,10 +10181,10 @@
     </row>
     <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C64" s="7" t="b">
         <v>0</v>
@@ -10203,10 +10198,10 @@
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C65" s="7" t="b">
         <v>1</v>
@@ -10220,10 +10215,10 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C66" s="7" t="b">
         <v>0</v>
@@ -10237,10 +10232,10 @@
     </row>
     <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C67" s="7" t="b">
         <v>0</v>
@@ -10254,10 +10249,10 @@
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -10271,10 +10266,10 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C69" s="7" t="b">
         <v>0</v>
@@ -10288,10 +10283,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>1</v>
@@ -10305,10 +10300,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -10322,10 +10317,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -10339,10 +10334,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -10356,10 +10351,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -10373,10 +10368,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -10390,10 +10385,10 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
@@ -10407,19 +10402,19 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C77" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" s="5" t="s">
         <v>861</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C77" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>862</v>
       </c>
       <c r="G77" s="7" t="b">
         <v>0</v>
@@ -10427,10 +10422,10 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
@@ -10444,10 +10439,10 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C79" s="7" t="b">
         <v>0</v>
@@ -10461,10 +10456,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -10478,10 +10473,10 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C81" s="7" t="b">
         <v>0</v>
@@ -10495,10 +10490,10 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>0</v>
@@ -10512,19 +10507,19 @@
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C83" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>403</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C83" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E83" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>404</v>
       </c>
       <c r="G83" s="7" t="b">
         <v>0</v>
@@ -10532,10 +10527,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -10549,10 +10544,10 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C85" s="7" t="b">
         <v>0</v>
@@ -10566,10 +10561,10 @@
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C86" s="7" t="b">
         <v>0</v>
@@ -10583,10 +10578,10 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C87" s="7" t="b">
         <v>0</v>
@@ -10600,10 +10595,10 @@
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C88" s="7" t="b">
         <v>0</v>
@@ -10617,10 +10612,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -10634,10 +10629,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -10651,10 +10646,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -10663,7 +10658,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G91" s="7" t="b">
         <v>0</v>
@@ -10671,10 +10666,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -10688,10 +10683,10 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
@@ -10705,10 +10700,10 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C94" s="7" t="b">
         <v>0</v>
@@ -10722,10 +10717,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -10739,10 +10734,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -10756,10 +10751,10 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>1</v>
@@ -10773,10 +10768,10 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>0</v>
@@ -10790,10 +10785,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>0</v>
@@ -10807,10 +10802,10 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C100" s="7" t="b">
         <v>0</v>
@@ -10819,7 +10814,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G100" s="7" t="b">
         <v>0</v>
@@ -10827,10 +10822,10 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C101" s="7" t="b">
         <v>0</v>
@@ -10844,10 +10839,10 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C102" s="7" t="b">
         <v>0</v>
@@ -10861,10 +10856,10 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C103" s="7" t="b">
         <v>0</v>
@@ -10878,10 +10873,10 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C104" s="7" t="b">
         <v>1</v>
@@ -10895,7 +10890,7 @@
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>165</v>
@@ -10912,7 +10907,7 @@
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>60</v>
@@ -10929,7 +10924,7 @@
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>60</v>
@@ -10946,7 +10941,7 @@
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>60</v>
@@ -10963,7 +10958,7 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>133</v>
@@ -10980,10 +10975,10 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C110" s="7" t="b">
         <v>0</v>
@@ -10997,10 +10992,10 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C111" s="7" t="b">
         <v>0</v>
@@ -11017,7 +11012,7 @@
         <v>222</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C112" s="7" t="b">
         <v>0</v>
@@ -11026,7 +11021,7 @@
         <v>1</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G112" s="7" t="b">
         <v>0</v>
@@ -11034,10 +11029,10 @@
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C113" s="7" t="b">
         <v>0</v>
@@ -11051,10 +11046,10 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B114" s="6" t="s">
         <v>436</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>437</v>
       </c>
       <c r="C114" s="7" t="b">
         <v>0</v>
@@ -11068,10 +11063,10 @@
     </row>
     <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C115" s="7" t="b">
         <v>0</v>
@@ -11085,10 +11080,10 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C116" s="7" t="b">
         <v>0</v>
@@ -11102,10 +11097,10 @@
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C117" s="7" t="b">
         <v>0</v>
@@ -11119,10 +11114,10 @@
     </row>
     <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C118" s="7" t="b">
         <v>0</v>
@@ -11136,19 +11131,19 @@
     </row>
     <row r="119" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C119" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E119" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C119" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E119" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F119" s="5" t="s">
-        <v>340</v>
       </c>
       <c r="G119" s="7" t="b">
         <v>0</v>
@@ -11156,10 +11151,10 @@
     </row>
     <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C120" s="7" t="b">
         <v>0</v>
@@ -11168,7 +11163,7 @@
         <v>1</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G120" s="7" t="b">
         <v>0</v>
@@ -11176,10 +11171,10 @@
     </row>
     <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C121" s="7" t="b">
         <v>0</v>
@@ -11193,10 +11188,10 @@
     </row>
     <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C122" s="7" t="b">
         <v>1</v>
@@ -11205,7 +11200,7 @@
         <v>1</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G122" s="7" t="b">
         <v>0</v>
@@ -11213,10 +11208,10 @@
     </row>
     <row r="123" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C123" s="7" t="b">
         <v>0</v>
@@ -11225,7 +11220,7 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G123" s="7" t="b">
         <v>0</v>
@@ -11233,10 +11228,10 @@
     </row>
     <row r="124" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C124" s="7" t="b">
         <v>0</v>
@@ -11250,10 +11245,10 @@
     </row>
     <row r="125" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C125" s="7" t="b">
         <v>0</v>
@@ -11267,10 +11262,10 @@
     </row>
     <row r="126" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C126" s="7" t="b">
         <v>0</v>
@@ -11284,10 +11279,10 @@
     </row>
     <row r="127" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C127" s="7" t="b">
         <v>0</v>
@@ -11301,10 +11296,10 @@
     </row>
     <row r="128" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C128" s="7" t="b">
         <v>0</v>
@@ -11313,7 +11308,7 @@
         <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G128" s="7" t="b">
         <v>0</v>
@@ -11321,10 +11316,10 @@
     </row>
     <row r="129" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C129" s="7" t="b">
         <v>0</v>
@@ -11338,10 +11333,10 @@
     </row>
     <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C130" s="7" t="b">
         <v>0</v>
@@ -11355,10 +11350,10 @@
     </row>
     <row r="131" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C131" s="7" t="b">
         <v>0</v>
@@ -11372,10 +11367,10 @@
     </row>
     <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C132" s="7" t="b">
         <v>0</v>
@@ -11389,10 +11384,10 @@
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C133" s="7" t="b">
         <v>0</v>
@@ -11406,10 +11401,10 @@
     </row>
     <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C134" s="7" t="b">
         <v>0</v>
@@ -11423,10 +11418,10 @@
     </row>
     <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C135" s="7" t="b">
         <v>0</v>
@@ -11440,10 +11435,10 @@
     </row>
     <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C136" s="7" t="b">
         <v>0</v>
@@ -11457,10 +11452,10 @@
     </row>
     <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C137" s="7" t="b">
         <v>0</v>
@@ -11474,10 +11469,10 @@
     </row>
     <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C138" s="7" t="b">
         <v>0</v>
@@ -11491,10 +11486,10 @@
     </row>
     <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C139" s="7" t="b">
         <v>0</v>
@@ -11508,10 +11503,10 @@
     </row>
     <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C140" s="7" t="b">
         <v>0</v>
@@ -11528,7 +11523,7 @@
         <v>95</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C141" s="7" t="b">
         <v>0</v>
@@ -11542,10 +11537,10 @@
     </row>
     <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C142" s="7" t="b">
         <v>0</v>
@@ -11559,10 +11554,10 @@
     </row>
     <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C143" s="7" t="b">
         <v>0</v>
@@ -11579,7 +11574,7 @@
         <v>96</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C144" s="7" t="b">
         <v>0</v>
@@ -11635,7 +11630,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -11643,10 +11638,10 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C2" s="7" t="b">
         <v>0</v>
@@ -11660,10 +11655,10 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C3" s="7" t="b">
         <v>0</v>
@@ -11677,10 +11672,10 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C4" s="7" t="b">
         <v>0</v>
@@ -11694,10 +11689,10 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C5" s="7" t="b">
         <v>1</v>
@@ -11711,10 +11706,10 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -11728,10 +11723,10 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -11745,10 +11740,10 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>0</v>
@@ -11762,10 +11757,10 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>818</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>819</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -11779,10 +11774,10 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -11796,10 +11791,10 @@
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C11" s="7" t="b">
         <v>1</v>
@@ -11813,10 +11808,10 @@
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C12" s="7" t="b">
         <v>0</v>
@@ -11830,10 +11825,10 @@
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C13" s="7" t="b">
         <v>0</v>
@@ -11847,10 +11842,10 @@
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C14" s="7" t="b">
         <v>0</v>
@@ -11864,10 +11859,10 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C15" s="7" t="b">
         <v>0</v>
@@ -11881,10 +11876,10 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C16" s="7" t="b">
         <v>0</v>
@@ -11898,10 +11893,10 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>775</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>776</v>
       </c>
       <c r="C17" s="7" t="b">
         <v>1</v>
@@ -11915,10 +11910,10 @@
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C18" s="7" t="b">
         <v>0</v>
@@ -11932,10 +11927,10 @@
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -11949,10 +11944,10 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C20" s="7" t="b">
         <v>0</v>
@@ -11966,10 +11961,10 @@
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>0</v>
@@ -11983,10 +11978,10 @@
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C22" s="7" t="b">
         <v>0</v>
@@ -12000,10 +11995,10 @@
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>821</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>822</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -12017,10 +12012,10 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C24" s="7" t="b">
         <v>0</v>
@@ -12034,10 +12029,10 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C25" s="7" t="b">
         <v>0</v>
@@ -12051,10 +12046,10 @@
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C26" s="7" t="b">
         <v>0</v>
@@ -12068,10 +12063,10 @@
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C27" s="7" t="b">
         <v>0</v>
@@ -12085,10 +12080,10 @@
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C28" s="7" t="b">
         <v>0</v>
@@ -12102,10 +12097,10 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C29" s="7" t="b">
         <v>0</v>
@@ -12119,10 +12114,10 @@
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C30" s="7" t="b">
         <v>0</v>
@@ -12136,10 +12131,10 @@
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C31" s="7" t="b">
         <v>0</v>
@@ -12148,7 +12143,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G31" s="7" t="b">
         <v>0</v>
@@ -12156,10 +12151,10 @@
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C32" s="7" t="b">
         <v>0</v>
@@ -12173,10 +12168,10 @@
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C33" s="7" t="b">
         <v>0</v>
@@ -12190,10 +12185,10 @@
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C34" s="7" t="b">
         <v>0</v>
@@ -12207,10 +12202,10 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C35" s="7" t="b">
         <v>0</v>
@@ -12224,10 +12219,10 @@
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C36" s="7" t="b">
         <v>1</v>
@@ -12241,10 +12236,10 @@
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C37" s="7" t="b">
         <v>0</v>
@@ -12258,10 +12253,10 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C38" s="7" t="b">
         <v>0</v>
@@ -12275,10 +12270,10 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C39" s="7" t="b">
         <v>0</v>
@@ -12292,10 +12287,10 @@
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C40" s="7" t="b">
         <v>0</v>
@@ -12309,10 +12304,10 @@
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C41" s="7" t="b">
         <v>0</v>
@@ -12326,10 +12321,10 @@
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C42" s="7" t="b">
         <v>0</v>
@@ -12343,10 +12338,10 @@
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C43" s="7" t="b">
         <v>0</v>
@@ -12360,10 +12355,10 @@
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C44" s="7" t="b">
         <v>0</v>
@@ -12377,10 +12372,10 @@
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C45" s="7" t="b">
         <v>0</v>
@@ -12394,10 +12389,10 @@
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C46" s="7" t="b">
         <v>0</v>
@@ -12411,10 +12406,10 @@
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C47" s="7" t="b">
         <v>0</v>
@@ -12428,10 +12423,10 @@
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C48" s="7" t="b">
         <v>0</v>
@@ -12445,10 +12440,10 @@
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>919</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>920</v>
       </c>
       <c r="C49" s="7" t="b">
         <v>0</v>
@@ -12462,10 +12457,10 @@
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C50" s="7" t="b">
         <v>0</v>
@@ -12479,10 +12474,10 @@
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C51" s="7" t="b">
         <v>0</v>
@@ -12496,10 +12491,10 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C52" s="7" t="b">
         <v>0</v>
@@ -12513,10 +12508,10 @@
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C53" s="7" t="b">
         <v>0</v>
@@ -12530,10 +12525,10 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C54" s="7" t="b">
         <v>0</v>
@@ -12547,10 +12542,10 @@
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C55" s="7" t="b">
         <v>0</v>
@@ -12564,10 +12559,10 @@
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>790</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>791</v>
       </c>
       <c r="C56" s="7" t="b">
         <v>0</v>
@@ -12581,10 +12576,10 @@
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>787</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>788</v>
       </c>
       <c r="C57" s="7" t="b">
         <v>0</v>
@@ -12598,10 +12593,10 @@
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C58" s="7" t="b">
         <v>0</v>
@@ -12615,10 +12610,10 @@
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C59" s="7" t="b">
         <v>0</v>
@@ -12632,10 +12627,10 @@
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>770</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>771</v>
       </c>
       <c r="C60" s="7" t="b">
         <v>0</v>
@@ -12649,10 +12644,10 @@
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>888</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>889</v>
       </c>
       <c r="C61" s="7" t="b">
         <v>0</v>
@@ -12666,10 +12661,10 @@
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C62" s="7" t="b">
         <v>0</v>
@@ -12683,10 +12678,10 @@
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C63" s="7" t="b">
         <v>0</v>
@@ -12700,10 +12695,10 @@
     </row>
     <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C64" s="7" t="b">
         <v>0</v>
@@ -12717,10 +12712,10 @@
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C65" s="7" t="b">
         <v>0</v>
@@ -12734,10 +12729,10 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C66" s="7" t="b">
         <v>0</v>
@@ -12751,10 +12746,10 @@
     </row>
     <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C67" s="7" t="b">
         <v>0</v>
@@ -12768,10 +12763,10 @@
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -12785,10 +12780,10 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C69" s="7" t="b">
         <v>0</v>
@@ -12802,10 +12797,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>0</v>
@@ -12819,10 +12814,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -12836,10 +12831,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -12853,10 +12848,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -12870,10 +12865,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -12887,10 +12882,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -12904,10 +12899,10 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
@@ -12921,10 +12916,10 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C77" s="7" t="b">
         <v>0</v>
@@ -12938,10 +12933,10 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
@@ -12955,10 +12950,10 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="C79" s="7" t="b">
         <v>0</v>
@@ -12972,10 +12967,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -12989,10 +12984,10 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C81" s="7" t="b">
         <v>0</v>
@@ -13006,10 +13001,10 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>0</v>
@@ -13023,10 +13018,10 @@
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C83" s="7" t="b">
         <v>0</v>
@@ -13040,10 +13035,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -13057,10 +13052,10 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C85" s="7" t="b">
         <v>0</v>
@@ -13074,10 +13069,10 @@
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C86" s="7" t="b">
         <v>0</v>
@@ -13091,10 +13086,10 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C87" s="7" t="b">
         <v>0</v>
@@ -13108,10 +13103,10 @@
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>772</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>773</v>
       </c>
       <c r="C88" s="7" t="b">
         <v>0</v>
@@ -13125,10 +13120,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -13142,10 +13137,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -13159,10 +13154,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -13176,10 +13171,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -13193,10 +13188,10 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
@@ -13205,7 +13200,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G93" s="7" t="b">
         <v>0</v>
@@ -13213,7 +13208,7 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>60</v>
@@ -13230,10 +13225,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -13247,10 +13242,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -13264,10 +13259,10 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>0</v>
@@ -13281,10 +13276,10 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>0</v>
@@ -13298,10 +13293,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>0</v>
@@ -13315,10 +13310,10 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C100" s="7" t="b">
         <v>0</v>
@@ -13332,10 +13327,10 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C101" s="7" t="b">
         <v>0</v>
@@ -13349,10 +13344,10 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C102" s="7" t="b">
         <v>0</v>
@@ -13361,7 +13356,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G102" s="7" t="b">
         <v>0</v>
@@ -13369,10 +13364,10 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C103" s="7" t="b">
         <v>0</v>
@@ -13386,10 +13381,10 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C104" s="7" t="b">
         <v>0</v>
@@ -13403,10 +13398,10 @@
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C105" s="7" t="b">
         <v>0</v>
@@ -13415,7 +13410,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G105" s="7" t="b">
         <v>0</v>
@@ -13423,10 +13418,10 @@
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C106" s="7" t="b">
         <v>0</v>
@@ -13440,10 +13435,10 @@
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C107" s="7" t="b">
         <v>0</v>
@@ -13457,10 +13452,10 @@
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C108" s="7" t="b">
         <v>0</v>
@@ -13474,10 +13469,10 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C109" s="7" t="b">
         <v>0</v>
@@ -13491,10 +13486,10 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C110" s="7" t="b">
         <v>0</v>
@@ -13508,10 +13503,10 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C111" s="7" t="b">
         <v>0</v>
@@ -13525,10 +13520,10 @@
     </row>
     <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C112" s="7" t="b">
         <v>0</v>
@@ -13542,10 +13537,10 @@
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C113" s="7" t="b">
         <v>0</v>
@@ -13559,10 +13554,10 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C114" s="7" t="b">
         <v>0</v>
@@ -13576,10 +13571,10 @@
     </row>
     <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C115" s="7" t="b">
         <v>0</v>
@@ -13593,10 +13588,10 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C116" s="7" t="b">
         <v>0</v>
@@ -13610,10 +13605,10 @@
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C117" s="7" t="b">
         <v>0</v>
@@ -13627,10 +13622,10 @@
     </row>
     <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C118" s="7" t="b">
         <v>0</v>
@@ -13687,7 +13682,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -13695,10 +13690,10 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C2" s="7" t="b">
         <v>0</v>
@@ -13712,10 +13707,10 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C3" s="7" t="b">
         <v>0</v>
@@ -13729,10 +13724,10 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C4" s="7" t="b">
         <v>0</v>
@@ -13746,10 +13741,10 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C5" s="7" t="b">
         <v>0</v>
@@ -13763,10 +13758,10 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -13780,10 +13775,10 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -13797,10 +13792,10 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>0</v>
@@ -13814,10 +13809,10 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -13831,10 +13826,10 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -13848,10 +13843,10 @@
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C11" s="7" t="b">
         <v>0</v>
@@ -13865,10 +13860,10 @@
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C12" s="7" t="b">
         <v>0</v>
@@ -13882,10 +13877,10 @@
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C13" s="7" t="b">
         <v>0</v>
@@ -13899,22 +13894,22 @@
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C14" s="7" t="b">
         <v>1</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E14" s="7" t="b">
         <v>1</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G14" s="7" t="b">
         <v>0</v>
@@ -13922,10 +13917,10 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C15" s="7" t="b">
         <v>0</v>
@@ -13939,10 +13934,10 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C16" s="7" t="b">
         <v>0</v>
@@ -13956,10 +13951,10 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C17" s="7" t="b">
         <v>0</v>
@@ -13973,10 +13968,10 @@
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C18" s="7" t="b">
         <v>0</v>
@@ -13990,10 +13985,10 @@
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -14007,10 +14002,10 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C20" s="7" t="b">
         <v>0</v>
@@ -14024,10 +14019,10 @@
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>0</v>
@@ -14041,10 +14036,10 @@
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C22" s="7" t="b">
         <v>0</v>
@@ -14058,10 +14053,10 @@
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -14075,10 +14070,10 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C24" s="7" t="b">
         <v>0</v>
@@ -14092,10 +14087,10 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>544</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>545</v>
       </c>
       <c r="C25" s="7" t="b">
         <v>0</v>
@@ -14109,10 +14104,10 @@
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C26" s="7" t="b">
         <v>0</v>
@@ -14126,10 +14121,10 @@
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C27" s="7" t="b">
         <v>0</v>
@@ -14143,10 +14138,10 @@
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C28" s="7" t="b">
         <v>0</v>
@@ -14160,10 +14155,10 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C29" s="7" t="b">
         <v>0</v>
@@ -14177,10 +14172,10 @@
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C30" s="7" t="b">
         <v>0</v>
@@ -14195,10 +14190,10 @@
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C31" s="7" t="b">
         <v>0</v>
@@ -14212,10 +14207,10 @@
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C32" s="7" t="b">
         <v>0</v>
@@ -14229,10 +14224,10 @@
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C33" s="7" t="b">
         <v>0</v>
@@ -14246,10 +14241,10 @@
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C34" s="7" t="b">
         <v>0</v>
@@ -14263,10 +14258,10 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C35" s="7" t="b">
         <v>0</v>
@@ -14280,10 +14275,10 @@
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C36" s="7" t="b">
         <v>0</v>
@@ -14297,10 +14292,10 @@
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C37" s="7" t="b">
         <v>0</v>
@@ -14314,10 +14309,10 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C38" s="7" t="b">
         <v>0</v>
@@ -14331,10 +14326,10 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C39" s="7" t="b">
         <v>0</v>
@@ -14348,10 +14343,10 @@
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C40" s="7" t="b">
         <v>0</v>
@@ -14365,10 +14360,10 @@
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C41" s="7" t="b">
         <v>0</v>
@@ -14382,10 +14377,10 @@
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C42" s="7" t="b">
         <v>0</v>
@@ -14399,10 +14394,10 @@
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C43" s="7" t="b">
         <v>0</v>
@@ -14416,10 +14411,10 @@
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C44" s="7" t="b">
         <v>0</v>
@@ -14433,10 +14428,10 @@
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C45" s="7" t="b">
         <v>0</v>
@@ -14450,10 +14445,10 @@
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C46" s="7" t="b">
         <v>0</v>
@@ -14467,10 +14462,10 @@
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C47" s="7" t="b">
         <v>0</v>
@@ -14484,10 +14479,10 @@
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C48" s="7" t="b">
         <v>0</v>
@@ -14501,10 +14496,10 @@
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C49" s="7" t="b">
         <v>0</v>
@@ -14518,10 +14513,10 @@
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C50" s="7" t="b">
         <v>0</v>
@@ -14535,10 +14530,10 @@
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C51" s="7" t="b">
         <v>0</v>
@@ -14552,10 +14547,10 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C52" s="7" t="b">
         <v>0</v>
@@ -14611,7 +14606,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -14619,10 +14614,10 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C2" s="7" t="b">
         <v>0</v>
@@ -14636,10 +14631,10 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C3" s="7" t="b">
         <v>0</v>
@@ -14653,10 +14648,10 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C4" s="7" t="b">
         <v>0</v>
@@ -14670,10 +14665,10 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C5" s="7" t="b">
         <v>0</v>
@@ -14687,10 +14682,10 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -14704,10 +14699,10 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -14721,10 +14716,10 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>0</v>
@@ -14738,10 +14733,10 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -14755,10 +14750,10 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -14772,10 +14767,10 @@
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C11" s="7" t="b">
         <v>0</v>
@@ -14789,10 +14784,10 @@
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C12" s="7" t="b">
         <v>0</v>
@@ -14806,10 +14801,10 @@
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C13" s="7" t="b">
         <v>0</v>
@@ -14823,10 +14818,10 @@
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C14" s="7" t="b">
         <v>0</v>
@@ -14840,10 +14835,10 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C15" s="7" t="b">
         <v>0</v>
@@ -14857,10 +14852,10 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C16" s="7" t="b">
         <v>0</v>
@@ -14874,10 +14869,10 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C17" s="7" t="b">
         <v>0</v>
@@ -14891,10 +14886,10 @@
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C18" s="7" t="b">
         <v>0</v>
@@ -14911,7 +14906,7 @@
         <v>148</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -14925,10 +14920,10 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C20" s="7" t="b">
         <v>0</v>
@@ -14942,10 +14937,10 @@
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>0</v>
@@ -14959,10 +14954,10 @@
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C22" s="7" t="b">
         <v>0</v>
@@ -14976,10 +14971,10 @@
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -14993,7 +14988,7 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>60</v>
@@ -15010,10 +15005,10 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C25" s="7" t="b">
         <v>0</v>
@@ -15027,10 +15022,10 @@
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C26" s="7" t="b">
         <v>0</v>
@@ -15044,10 +15039,10 @@
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C27" s="7" t="b">
         <v>0</v>
@@ -15061,10 +15056,10 @@
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C28" s="7" t="b">
         <v>0</v>
@@ -15078,10 +15073,10 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C29" s="7" t="b">
         <v>0</v>
@@ -15095,10 +15090,10 @@
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C30" s="7" t="b">
         <v>0</v>
@@ -15112,10 +15107,10 @@
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C31" s="7" t="b">
         <v>0</v>
@@ -15129,10 +15124,10 @@
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C32" s="7" t="b">
         <v>0</v>
@@ -15146,10 +15141,10 @@
     </row>
     <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C33" s="7" t="b">
         <v>0</v>
@@ -15163,10 +15158,10 @@
     </row>
     <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C34" s="7" t="b">
         <v>1</v>
@@ -15180,10 +15175,10 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C35" s="7" t="b">
         <v>0</v>
@@ -15197,10 +15192,10 @@
     </row>
     <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C36" s="7" t="b">
         <v>0</v>
@@ -15214,10 +15209,10 @@
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C37" s="7" t="b">
         <v>0</v>
@@ -15231,10 +15226,10 @@
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C38" s="7" t="b">
         <v>0</v>
@@ -15248,10 +15243,10 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C39" s="7" t="b">
         <v>0</v>
@@ -15265,10 +15260,10 @@
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C40" s="7" t="b">
         <v>0</v>
@@ -15282,10 +15277,10 @@
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C41" s="7" t="b">
         <v>0</v>
@@ -15299,10 +15294,10 @@
     </row>
     <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C42" s="7" t="b">
         <v>0</v>
@@ -15316,10 +15311,10 @@
     </row>
     <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C43" s="7" t="b">
         <v>0</v>
@@ -15333,10 +15328,10 @@
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C44" s="7" t="b">
         <v>1</v>
@@ -15350,10 +15345,10 @@
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C45" s="7" t="b">
         <v>0</v>
@@ -15367,10 +15362,10 @@
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C46" s="7" t="b">
         <v>0</v>
@@ -15384,10 +15379,10 @@
     </row>
     <row r="47" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C47" s="7" t="b">
         <v>0</v>
@@ -15401,10 +15396,10 @@
     </row>
     <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C48" s="7" t="b">
         <v>0</v>
@@ -15418,10 +15413,10 @@
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C49" s="7" t="b">
         <v>0</v>
@@ -15430,7 +15425,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G49" s="7" t="b">
         <v>0</v>
@@ -15438,10 +15433,10 @@
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C50" s="7" t="b">
         <v>0</v>
@@ -15455,10 +15450,10 @@
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C51" s="7" t="b">
         <v>0</v>
@@ -15475,7 +15470,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C52" s="7" t="b">
         <v>0</v>
@@ -15489,10 +15484,10 @@
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C53" s="7" t="b">
         <v>1</v>
@@ -15506,10 +15501,10 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C54" s="7" t="b">
         <v>0</v>
@@ -15523,10 +15518,10 @@
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C55" s="7" t="b">
         <v>0</v>
@@ -15540,10 +15535,10 @@
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C56" s="7" t="b">
         <v>0</v>
@@ -15557,10 +15552,10 @@
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C57" s="7" t="b">
         <v>0</v>
@@ -15574,10 +15569,10 @@
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C58" s="7" t="b">
         <v>0</v>
@@ -15591,10 +15586,10 @@
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C59" s="7" t="b">
         <v>0</v>
@@ -15608,10 +15603,10 @@
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C60" s="7" t="b">
         <v>0</v>
@@ -15625,10 +15620,10 @@
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C61" s="7" t="b">
         <v>0</v>
@@ -15642,10 +15637,10 @@
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C62" s="7" t="b">
         <v>0</v>
@@ -15659,10 +15654,10 @@
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C63" s="7" t="b">
         <v>0</v>
@@ -15676,10 +15671,10 @@
     </row>
     <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C64" s="7" t="b">
         <v>0</v>
@@ -15693,10 +15688,10 @@
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C65" s="7" t="b">
         <v>0</v>
@@ -15710,10 +15705,10 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C66" s="7" t="b">
         <v>0</v>
@@ -15727,16 +15722,16 @@
     </row>
     <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C67" s="7" t="b">
         <v>1</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E67" s="7" t="b">
         <v>0</v>
@@ -15747,10 +15742,10 @@
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -15767,7 +15762,7 @@
         <v>118</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C69" s="7" t="b">
         <v>0</v>
@@ -15781,10 +15776,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>0</v>
@@ -15798,10 +15793,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -15815,10 +15810,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -15832,10 +15827,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -15849,10 +15844,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -15866,10 +15861,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -15883,10 +15878,10 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
@@ -15900,10 +15895,10 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C77" s="7" t="b">
         <v>0</v>
@@ -15917,10 +15912,10 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
@@ -15934,10 +15929,10 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>537</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>538</v>
       </c>
       <c r="C79" s="7" t="b">
         <v>0</v>
@@ -15951,10 +15946,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -15968,10 +15963,10 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C81" s="7" t="b">
         <v>0</v>
@@ -15985,10 +15980,10 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>0</v>
@@ -16002,10 +15997,10 @@
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C83" s="7" t="b">
         <v>0</v>
@@ -16019,10 +16014,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -16036,7 +16031,7 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>60</v>
@@ -16056,7 +16051,7 @@
         <v>29</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C86" s="7" t="b">
         <v>0</v>
@@ -16070,10 +16065,10 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C87" s="7" t="b">
         <v>0</v>
@@ -16087,10 +16082,10 @@
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C88" s="7" t="b">
         <v>0</v>
@@ -16104,10 +16099,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -16121,10 +16116,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -16138,10 +16133,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -16155,10 +16150,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -16172,10 +16167,10 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
@@ -16189,10 +16184,10 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C94" s="7" t="b">
         <v>0</v>
@@ -16206,10 +16201,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -16223,10 +16218,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -16240,10 +16235,10 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>0</v>
@@ -16257,10 +16252,10 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>0</v>
@@ -16274,10 +16269,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>0</v>
@@ -16333,7 +16328,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -16341,10 +16336,10 @@
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C2" s="7" t="b">
         <v>1</v>
@@ -16358,10 +16353,10 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C3" s="7" t="b">
         <v>1</v>
@@ -16375,10 +16370,10 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C4" s="7" t="b">
         <v>0</v>
@@ -16392,10 +16387,10 @@
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C5" s="7" t="b">
         <v>1</v>
@@ -16409,10 +16404,10 @@
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C6" s="7" t="b">
         <v>0</v>
@@ -16426,10 +16421,10 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -16443,10 +16438,10 @@
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C8" s="7" t="b">
         <v>1</v>
@@ -16460,10 +16455,10 @@
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -16477,10 +16472,10 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -16494,10 +16489,10 @@
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C11" s="7" t="b">
         <v>0</v>
@@ -16511,10 +16506,10 @@
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C12" s="7" t="b">
         <v>0</v>
@@ -16528,10 +16523,10 @@
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C13" s="7" t="b">
         <v>0</v>
@@ -16545,10 +16540,10 @@
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C14" s="7" t="b">
         <v>0</v>
@@ -16562,10 +16557,10 @@
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C15" s="7" t="b">
         <v>0</v>
@@ -16579,10 +16574,10 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C16" s="7" t="b">
         <v>0</v>
@@ -16596,10 +16591,10 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C17" s="7" t="b">
         <v>0</v>
@@ -16613,10 +16608,10 @@
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C18" s="7" t="b">
         <v>0</v>
@@ -16630,10 +16625,10 @@
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C19" s="7" t="b">
         <v>0</v>
@@ -16647,10 +16642,10 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C20" s="7" t="b">
         <v>0</v>
@@ -16664,10 +16659,10 @@
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C21" s="7" t="b">
         <v>1</v>
@@ -16681,10 +16676,10 @@
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C22" s="7" t="b">
         <v>0</v>
@@ -16698,10 +16693,10 @@
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C23" s="7" t="b">
         <v>0</v>
@@ -16715,10 +16710,10 @@
     </row>
     <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C24" s="7" t="b">
         <v>0</v>
@@ -16732,10 +16727,10 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C25" s="7" t="b">
         <v>1</v>
@@ -16749,10 +16744,10 @@
     </row>
     <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C26" s="7" t="b">
         <v>0</v>
@@ -16766,10 +16761,10 @@
     </row>
     <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C27" s="7" t="b">
         <v>1</v>
@@ -16783,10 +16778,10 @@
     </row>
     <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C28" s="7" t="b">
         <v>1</v>
@@ -16800,10 +16795,10 @@
     </row>
     <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C29" s="7" t="b">
         <v>1</v>
@@ -16817,10 +16812,10 @@
     </row>
     <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C30" s="7" t="b">
         <v>0</v>
@@ -16834,10 +16829,10 @@
     </row>
     <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C31" s="7" t="b">
         <v>1</v>
@@ -16851,10 +16846,10 @@
     </row>
     <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C32" s="7" t="b">
         <v>0</v>
@@ -16868,10 +16863,10 @@
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>603</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>604</v>
       </c>
       <c r="C33" s="7" t="b">
         <v>0</v>
@@ -16885,10 +16880,10 @@
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C34" s="7" t="b">
         <v>0</v>
@@ -16902,10 +16897,10 @@
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C35" s="7" t="b">
         <v>0</v>
@@ -16919,10 +16914,10 @@
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C36" s="7" t="b">
         <v>0</v>
@@ -16936,10 +16931,10 @@
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C37" s="7" t="b">
         <v>0</v>
@@ -16953,10 +16948,10 @@
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C38" s="7" t="b">
         <v>0</v>
@@ -16970,10 +16965,10 @@
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C39" s="7" t="b">
         <v>0</v>
@@ -16987,10 +16982,10 @@
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C40" s="7" t="b">
         <v>0</v>
@@ -17004,10 +16999,10 @@
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C41" s="7" t="b">
         <v>0</v>
@@ -17021,10 +17016,10 @@
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C42" s="7" t="b">
         <v>1</v>
@@ -17038,10 +17033,10 @@
     </row>
     <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C43" s="7" t="b">
         <v>0</v>
@@ -17055,10 +17050,10 @@
     </row>
     <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C44" s="7" t="b">
         <v>0</v>
@@ -17072,10 +17067,10 @@
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C45" s="7" t="b">
         <v>1</v>
@@ -17089,30 +17084,30 @@
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="C46" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>949</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="C46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C47" s="7" t="b">
         <v>0</v>
@@ -17126,10 +17121,10 @@
     </row>
     <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C48" s="7" t="b">
         <v>0</v>
@@ -17143,10 +17138,10 @@
     </row>
     <row r="49" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C49" s="7" t="b">
         <v>0</v>
@@ -17160,10 +17155,10 @@
     </row>
     <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C50" s="7" t="b">
         <v>0</v>
@@ -17177,10 +17172,10 @@
     </row>
     <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C51" s="7" t="b">
         <v>0</v>
@@ -17194,10 +17189,10 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C52" s="7" t="b">
         <v>0</v>
@@ -17211,10 +17206,10 @@
     </row>
     <row r="53" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>637</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>638</v>
       </c>
       <c r="C53" s="7" t="b">
         <v>1</v>
@@ -17228,10 +17223,10 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C54" s="7" t="b">
         <v>0</v>
@@ -17245,10 +17240,10 @@
     </row>
     <row r="55" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C55" s="7" t="b">
         <v>1</v>
@@ -17262,10 +17257,10 @@
     </row>
     <row r="56" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C56" s="7" t="b">
         <v>0</v>
@@ -17279,10 +17274,10 @@
     </row>
     <row r="57" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C57" s="7" t="b">
         <v>0</v>
@@ -17296,10 +17291,10 @@
     </row>
     <row r="58" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C58" s="7" t="b">
         <v>1</v>
@@ -17313,10 +17308,10 @@
     </row>
     <row r="59" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C59" s="7" t="b">
         <v>0</v>
@@ -17330,10 +17325,10 @@
     </row>
     <row r="60" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C60" s="7" t="b">
         <v>0</v>
@@ -17342,7 +17337,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G60" s="7" t="b">
         <v>0</v>
@@ -17350,10 +17345,10 @@
     </row>
     <row r="61" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C61" s="7" t="b">
         <v>0</v>
@@ -17367,10 +17362,10 @@
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C62" s="7" t="b">
         <v>1</v>
@@ -17384,10 +17379,10 @@
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C63" s="7" t="b">
         <v>0</v>
@@ -17401,10 +17396,10 @@
     </row>
     <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C64" s="7" t="b">
         <v>1</v>
@@ -17418,10 +17413,10 @@
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C65" s="7" t="b">
         <v>0</v>
@@ -17435,10 +17430,10 @@
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C66" s="7" t="b">
         <v>0</v>
@@ -17452,10 +17447,10 @@
     </row>
     <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C67" s="7" t="b">
         <v>0</v>
@@ -17469,10 +17464,10 @@
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -17486,10 +17481,10 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C69" s="7" t="b">
         <v>0</v>
@@ -17503,10 +17498,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>0</v>
@@ -17520,10 +17515,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -17537,10 +17532,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -17554,10 +17549,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -17571,10 +17566,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -17588,10 +17583,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -17605,10 +17600,10 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
@@ -17622,10 +17617,10 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C77" s="7" t="b">
         <v>0</v>
@@ -17639,10 +17634,10 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
@@ -17656,10 +17651,10 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C79" s="7" t="b">
         <v>0</v>
@@ -17673,10 +17668,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -17690,10 +17685,10 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C81" s="7" t="b">
         <v>0</v>
@@ -17707,10 +17702,10 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>1</v>
@@ -17724,10 +17719,10 @@
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C83" s="7" t="b">
         <v>0</v>
@@ -17741,10 +17736,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -17758,10 +17753,10 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C85" s="7" t="b">
         <v>0</v>
@@ -17775,10 +17770,10 @@
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C86" s="7" t="b">
         <v>0</v>
@@ -17792,10 +17787,10 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C87" s="7" t="b">
         <v>0</v>
@@ -17809,10 +17804,10 @@
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C88" s="7" t="b">
         <v>0</v>
@@ -17826,10 +17821,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -17843,10 +17838,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -17860,10 +17855,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -17877,10 +17872,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -17894,10 +17889,10 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
@@ -17911,10 +17906,10 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C94" s="7" t="b">
         <v>0</v>
@@ -17928,10 +17923,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -17945,10 +17940,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -17962,10 +17957,10 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>0</v>
@@ -17979,10 +17974,10 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>1</v>
@@ -17996,10 +17991,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>1</v>
@@ -18013,10 +18008,10 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C100" s="7" t="b">
         <v>1</v>
@@ -18030,10 +18025,10 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C101" s="7" t="b">
         <v>0</v>
@@ -18047,10 +18042,10 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C102" s="7" t="b">
         <v>0</v>
@@ -18064,10 +18059,10 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C103" s="7" t="b">
         <v>0</v>
@@ -18081,10 +18076,10 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C104" s="7" t="b">
         <v>0</v>
@@ -18098,10 +18093,10 @@
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C105" s="7" t="b">
         <v>0</v>
@@ -18115,10 +18110,10 @@
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C106" s="7" t="b">
         <v>0</v>
@@ -18132,10 +18127,10 @@
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C107" s="7" t="b">
         <v>0</v>
@@ -18149,10 +18144,10 @@
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C108" s="7" t="b">
         <v>0</v>
@@ -18166,10 +18161,10 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C109" s="7" t="b">
         <v>0</v>
@@ -18183,10 +18178,10 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C110" s="7" t="b">
         <v>0</v>
@@ -18200,10 +18195,10 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C111" s="7" t="b">
         <v>0</v>
@@ -18217,10 +18212,10 @@
     </row>
     <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C112" s="7" t="b">
         <v>0</v>
@@ -18234,10 +18229,10 @@
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C113" s="7" t="b">
         <v>0</v>
@@ -18246,7 +18241,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G113" s="7" t="b">
         <v>0</v>
@@ -18254,10 +18249,10 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C114" s="7" t="b">
         <v>0</v>
@@ -18272,10 +18267,10 @@
     </row>
     <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C115" s="7" t="b">
         <v>0</v>
@@ -18289,10 +18284,10 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C116" s="7" t="b">
         <v>0</v>
@@ -18306,10 +18301,10 @@
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C117" s="7" t="b">
         <v>0</v>
@@ -18323,10 +18318,10 @@
     </row>
     <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C118" s="7" t="b">
         <v>0</v>
@@ -18340,10 +18335,10 @@
     </row>
     <row r="119" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C119" s="7" t="b">
         <v>0</v>
@@ -18357,10 +18352,10 @@
     </row>
     <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C120" s="7" t="b">
         <v>0</v>
@@ -18374,10 +18369,10 @@
     </row>
     <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C121" s="7" t="b">
         <v>0</v>
@@ -18391,10 +18386,10 @@
     </row>
     <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C122" s="7" t="b">
         <v>0</v>
@@ -18408,10 +18403,10 @@
     </row>
     <row r="123" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C123" s="7" t="b">
         <v>0</v>
@@ -18425,10 +18420,10 @@
     </row>
     <row r="124" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C124" s="7" t="b">
         <v>0</v>
@@ -18442,10 +18437,10 @@
     </row>
     <row r="125" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C125" s="7" t="b">
         <v>0</v>
@@ -18459,10 +18454,10 @@
     </row>
     <row r="126" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C126" s="7" t="b">
         <v>0</v>
@@ -18476,10 +18471,10 @@
     </row>
     <row r="127" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C127" s="7" t="b">
         <v>0</v>
@@ -18493,10 +18488,10 @@
     </row>
     <row r="128" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C128" s="7" t="b">
         <v>1</v>
@@ -18510,10 +18505,10 @@
     </row>
     <row r="129" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C129" s="7" t="b">
         <v>1</v>
@@ -18527,10 +18522,10 @@
     </row>
     <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C130" s="7" t="b">
         <v>0</v>
@@ -18544,10 +18539,10 @@
     </row>
     <row r="131" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C131" s="7" t="b">
         <v>0</v>
@@ -18561,10 +18556,10 @@
     </row>
     <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C132" s="7" t="b">
         <v>0</v>
@@ -18578,10 +18573,10 @@
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C133" s="7" t="b">
         <v>0</v>
@@ -18595,10 +18590,10 @@
     </row>
     <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C134" s="7" t="b">
         <v>0</v>
@@ -18612,10 +18607,10 @@
     </row>
     <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C135" s="7" t="b">
         <v>0</v>
@@ -18629,10 +18624,10 @@
     </row>
     <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C136" s="7" t="b">
         <v>1</v>
@@ -18646,10 +18641,10 @@
     </row>
     <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C137" s="7" t="b">
         <v>0</v>
@@ -18663,10 +18658,10 @@
     </row>
     <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C138" s="7" t="b">
         <v>0</v>
@@ -18680,10 +18675,10 @@
     </row>
     <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C139" s="7" t="b">
         <v>0</v>
@@ -18697,10 +18692,10 @@
     </row>
     <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C140" s="7" t="b">
         <v>0</v>
@@ -18714,10 +18709,10 @@
     </row>
     <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C141" s="7" t="b">
         <v>0</v>
@@ -18731,10 +18726,10 @@
     </row>
     <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C142" s="7" t="b">
         <v>0</v>
@@ -18748,10 +18743,10 @@
     </row>
     <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C143" s="7" t="b">
         <v>0</v>
@@ -18765,10 +18760,10 @@
     </row>
     <row r="144" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C144" s="7" t="b">
         <v>0</v>
@@ -18782,10 +18777,10 @@
     </row>
     <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C145" s="7" t="b">
         <v>0</v>
@@ -18799,10 +18794,10 @@
     </row>
     <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C146" s="7" t="b">
         <v>0</v>
@@ -18816,10 +18811,10 @@
     </row>
     <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C147" s="7" t="b">
         <v>0</v>
@@ -18833,10 +18828,10 @@
     </row>
     <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C148" s="7" t="b">
         <v>0</v>
@@ -18850,10 +18845,10 @@
     </row>
     <row r="149" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C149" s="7" t="b">
         <v>0</v>
@@ -18867,10 +18862,10 @@
     </row>
     <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C150" s="7" t="b">
         <v>0</v>
@@ -18884,10 +18879,10 @@
     </row>
     <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C151" s="7" t="b">
         <v>0</v>
@@ -18901,10 +18896,10 @@
     </row>
     <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C152" s="7" t="b">
         <v>0</v>
@@ -18918,10 +18913,10 @@
     </row>
     <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C153" s="7" t="b">
         <v>0</v>
@@ -18935,10 +18930,10 @@
     </row>
     <row r="154" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C154" s="7" t="b">
         <v>0</v>
@@ -18952,10 +18947,10 @@
     </row>
     <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C155" s="7" t="b">
         <v>0</v>
@@ -18972,7 +18967,7 @@
         <v>118</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C156" s="7" t="b">
         <v>0</v>
@@ -18986,10 +18981,10 @@
     </row>
     <row r="157" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C157" s="7" t="b">
         <v>1</v>
@@ -19003,10 +18998,10 @@
     </row>
     <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C158" s="7" t="b">
         <v>0</v>
@@ -19020,10 +19015,10 @@
     </row>
     <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C159" s="7" t="b">
         <v>0</v>
@@ -19037,10 +19032,10 @@
     </row>
     <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C160" s="7" t="b">
         <v>1</v>
@@ -19054,10 +19049,10 @@
     </row>
     <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="5" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C161" s="7" t="b">
         <v>1</v>
@@ -19071,10 +19066,10 @@
     </row>
     <row r="162" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C162" s="7" t="b">
         <v>1</v>
@@ -19088,10 +19083,10 @@
     </row>
     <row r="163" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C163" s="7" t="b">
         <v>0</v>
@@ -19105,10 +19100,10 @@
     </row>
     <row r="164" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C164" s="7" t="b">
         <v>0</v>
